--- a/artfynd/A 21662-2022 artfynd.xlsx
+++ b/artfynd/A 21662-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 21662-2022 artfynd.xlsx
+++ b/artfynd/A 21662-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1233,6 +1233,215 @@
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>124128891</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79869</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Lunglav, Mpd</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>596126</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6928361</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Sättna</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-04-16</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-04-16</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>124120714</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57507</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Spillkråka, Mpd</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>595866</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6928388</v>
+      </c>
+      <c r="S8" t="n">
+        <v>20</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Sättna</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-04-16</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-04-16</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 21662-2022 artfynd.xlsx
+++ b/artfynd/A 21662-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1442,6 +1442,2008 @@
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>124201987</v>
+      </c>
+      <c r="B9" t="n">
+        <v>90990</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Ullticka, Mpd</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>596125</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6928376</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Sättna</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-04-18</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-04-18</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>124186575</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79869</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Lynglav, Mpd</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>596036</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6928364</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Sättna</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-04-18</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-04-18</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>124193487</v>
+      </c>
+      <c r="B11" t="n">
+        <v>98079</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Garnlav , Mpd</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>595943</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6928393</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Sättna</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-04-18</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-04-18</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>124206962</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57658</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>266237</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Talltita x tofsmes</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Poecile montanus x Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Större hackspett , Mpd</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>596168</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6928357</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Sättna</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-04-18</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-04-18</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>124199083</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57861</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Kungsfågel, Mpd</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>596036</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6928364</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Sättna</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-04-18</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-04-18</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>124189689</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57926</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>102999</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Björktrast</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Turdus pilaris</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Björktrast, Mpd</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>595952</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6928371</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Sättna</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-04-18</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-04-18</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>124193338</v>
+      </c>
+      <c r="B15" t="n">
+        <v>56700</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Tjäder , Mpd</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>595945</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6928357</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Sättna</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-04-18</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-04-18</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>124199280</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57644</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Talltita, Mpd</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>596095</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6928397</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Sättna</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-04-18</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-04-18</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>124197321</v>
+      </c>
+      <c r="B17" t="n">
+        <v>78789</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>230405</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Garnlav (ssp. sarmentosa)</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>garnlav , Mpd</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>596021</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6928323</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Sättna</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-04-18</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>13:18</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-04-18</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>13:18</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>124193153</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57644</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Talltita , Mpd</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>595923</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6928341</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Sättna</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-04-18</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-04-18</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Kan höras I träden.</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>124201656</v>
+      </c>
+      <c r="B19" t="n">
+        <v>56692</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Järpebajs, Mpd</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>596201</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6928367</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Sättna</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-04-18</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-04-18</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Spillning</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Dropping</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>124185717</v>
+      </c>
+      <c r="B20" t="n">
+        <v>78789</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>230405</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Garnlav (ssp. sarmentosa)</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Garnlav , Mpd</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>595943</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6928393</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Sättna</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-04-18</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>09:33</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-04-18</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>09:33</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>124191655</v>
+      </c>
+      <c r="B21" t="n">
+        <v>56700</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Tjäder , Mpd</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>595903</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6928353</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Sättna</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-04-18</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-04-18</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>124198508</v>
+      </c>
+      <c r="B22" t="n">
+        <v>56700</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Tjäderfjäder, Mpd</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>596067</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6928345</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Sättna</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-04-18</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-04-18</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Hår, päls, fjäll eller fjädrar</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Hair, fur, scale or feather</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>124188895</v>
+      </c>
+      <c r="B23" t="n">
+        <v>57920</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>103001</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Rödvingetrast</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Turdus iliacus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Rödvingetrast, Mpd</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>595997</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6928324</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Sättna</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-04-18</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-04-18</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>124201216</v>
+      </c>
+      <c r="B24" t="n">
+        <v>56692</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Järpe , Mpd</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>596199</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6928355</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Sättna</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-04-18</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>14:42</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-04-18</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>14:42</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>124185899</v>
+      </c>
+      <c r="B25" t="n">
+        <v>90955</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Vedticka, Mpd</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>596036</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6928364</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Sättna</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-04-18</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-04-18</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>124192837</v>
+      </c>
+      <c r="B26" t="n">
+        <v>56700</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Talltita , Mpd</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>595923</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6928341</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Sättna</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-04-18</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-04-18</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 21662-2022 artfynd.xlsx
+++ b/artfynd/A 21662-2022 artfynd.xlsx
@@ -1444,10 +1444,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124185717</v>
+        <v>124186575</v>
       </c>
       <c r="B9" t="n">
-        <v>78811</v>
+        <v>79891</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1460,34 +1460,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>230405</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Garnlav , Mpd</t>
+          <t>Lynglav, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>595943</v>
+        <v>596036</v>
       </c>
       <c r="R9" t="n">
-        <v>6928393</v>
+        <v>6928364</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1517,19 +1517,9 @@
           <t>2025-04-18</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>09:33</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-04-18</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>09:33</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1544,22 +1534,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124199280</v>
+        <v>124198508</v>
       </c>
       <c r="B10" t="n">
-        <v>57666</v>
+        <v>56722</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1568,43 +1558,48 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>hane</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Talltita, Mpd</t>
+          <t>Tjäderfjäder, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>596095</v>
+        <v>596067</v>
       </c>
       <c r="R10" t="n">
-        <v>6928397</v>
+        <v>6928345</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1647,6 +1642,16 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Hår, päls, fjäll eller fjädrar</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Hair, fur, scale or feather</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1663,10 +1668,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124189689</v>
+        <v>124199083</v>
       </c>
       <c r="B11" t="n">
-        <v>57948</v>
+        <v>57883</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1675,43 +1680,43 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102999</v>
+        <v>103015</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Björktrast, Mpd</t>
+          <t>Kungsfågel, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>595952</v>
+        <v>596036</v>
       </c>
       <c r="R11" t="n">
-        <v>6928371</v>
+        <v>6928364</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1770,10 +1775,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124186575</v>
+        <v>124197321</v>
       </c>
       <c r="B12" t="n">
-        <v>79891</v>
+        <v>78811</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1786,34 +1791,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>230405</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Lynglav, Mpd</t>
+          <t>garnlav , Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>596036</v>
+        <v>596021</v>
       </c>
       <c r="R12" t="n">
-        <v>6928364</v>
+        <v>6928323</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1843,9 +1848,19 @@
           <t>2025-04-18</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>13:18</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-04-18</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1860,22 +1875,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124188895</v>
+        <v>124193338</v>
       </c>
       <c r="B13" t="n">
-        <v>57942</v>
+        <v>56722</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1884,43 +1899,43 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103001</v>
+        <v>100138</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Rödvingetrast, Mpd</t>
+          <t>Tjäder , Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>595997</v>
+        <v>595945</v>
       </c>
       <c r="R13" t="n">
-        <v>6928324</v>
+        <v>6928357</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1950,9 +1965,19 @@
           <t>2025-04-18</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-04-18</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1967,19 +1992,19 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124193338</v>
+        <v>124191655</v>
       </c>
       <c r="B14" t="n">
         <v>56722</v>
@@ -2024,10 +2049,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>595945</v>
+        <v>595903</v>
       </c>
       <c r="R14" t="n">
-        <v>6928357</v>
+        <v>6928353</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2059,7 +2084,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2069,7 +2094,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2198,10 +2223,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124201216</v>
+        <v>124193487</v>
       </c>
       <c r="B16" t="n">
-        <v>56714</v>
+        <v>98101</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2210,43 +2235,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Järpe , Mpd</t>
+          <t>Garnlav , Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>596199</v>
+        <v>595943</v>
       </c>
       <c r="R16" t="n">
-        <v>6928355</v>
+        <v>6928393</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2278,7 +2298,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2288,7 +2308,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2315,10 +2335,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124206962</v>
+        <v>124192837</v>
       </c>
       <c r="B17" t="n">
-        <v>57680</v>
+        <v>56722</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2331,40 +2351,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>266237</v>
+        <v>100138</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltita x tofsmes</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile montanus x Lophophanes cristatus</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr"/>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Större hackspett , Mpd</t>
+          <t>Talltita , Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>596168</v>
+        <v>595923</v>
       </c>
       <c r="R17" t="n">
-        <v>6928357</v>
+        <v>6928341</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2396,7 +2410,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2406,7 +2420,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2433,10 +2447,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124193487</v>
+        <v>124201216</v>
       </c>
       <c r="B18" t="n">
-        <v>98101</v>
+        <v>56714</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2445,38 +2459,43 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Garnlav , Mpd</t>
+          <t>Järpe , Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>595943</v>
+        <v>596199</v>
       </c>
       <c r="R18" t="n">
-        <v>6928393</v>
+        <v>6928355</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2508,7 +2527,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2518,7 +2537,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2545,10 +2564,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124197321</v>
+        <v>124185899</v>
       </c>
       <c r="B19" t="n">
-        <v>78811</v>
+        <v>90977</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2557,38 +2576,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>230405</v>
+        <v>5447</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>garnlav , Mpd</t>
+          <t>Vedticka, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>596021</v>
+        <v>596036</v>
       </c>
       <c r="R19" t="n">
-        <v>6928323</v>
+        <v>6928364</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2618,19 +2637,9 @@
           <t>2025-04-18</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>13:18</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-04-18</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>13:18</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2645,22 +2654,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124185899</v>
+        <v>124191705</v>
       </c>
       <c r="B20" t="n">
-        <v>90977</v>
+        <v>57666</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2669,38 +2678,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5447</v>
+        <v>103021</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Vedticka, Mpd</t>
+          <t>Talltita , Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>596036</v>
+        <v>595923</v>
       </c>
       <c r="R20" t="n">
-        <v>6928364</v>
+        <v>6928341</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2730,9 +2739,24 @@
           <t>2025-04-18</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>11:42</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-04-18</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>11:42</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>2 talltita kan höras i träden</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2747,22 +2771,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124201656</v>
+        <v>124206962</v>
       </c>
       <c r="B21" t="n">
-        <v>56714</v>
+        <v>57680</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2771,38 +2795,44 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>102612</v>
+        <v>266237</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Talltita x tofsmes</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Poecile montanus x Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Järpebajs, Mpd</t>
+          <t>Större hackspett , Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>596201</v>
+        <v>596168</v>
       </c>
       <c r="R21" t="n">
-        <v>6928367</v>
+        <v>6928357</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2832,11 +2862,21 @@
           <t>2025-04-18</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-04-18</t>
         </is>
       </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -2845,36 +2885,26 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>Spillning</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Dropping</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124199083</v>
+        <v>124199280</v>
       </c>
       <c r="B22" t="n">
-        <v>57883</v>
+        <v>57666</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2883,43 +2913,43 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Kungsfågel, Mpd</t>
+          <t>Talltita, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>596036</v>
+        <v>596095</v>
       </c>
       <c r="R22" t="n">
-        <v>6928364</v>
+        <v>6928397</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2978,10 +3008,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124192837</v>
+        <v>124189689</v>
       </c>
       <c r="B23" t="n">
-        <v>56722</v>
+        <v>57948</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2990,20 +3020,20 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100138</v>
+        <v>102999</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3012,16 +3042,21 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Talltita , Mpd</t>
+          <t>Björktrast, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>595923</v>
+        <v>595952</v>
       </c>
       <c r="R23" t="n">
-        <v>6928341</v>
+        <v>6928371</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3051,19 +3086,9 @@
           <t>2025-04-18</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>12:01</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-04-18</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>12:01</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3078,22 +3103,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124198508</v>
+        <v>124185717</v>
       </c>
       <c r="B24" t="n">
-        <v>56722</v>
+        <v>78811</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3102,48 +3127,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100138</v>
+        <v>230405</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Tjäderfjäder, Mpd</t>
+          <t>Garnlav , Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>596067</v>
+        <v>595943</v>
       </c>
       <c r="R24" t="n">
-        <v>6928345</v>
+        <v>6928393</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3173,11 +3188,21 @@
           <t>2025-04-18</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>09:33</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-04-18</t>
         </is>
       </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>09:33</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3186,36 +3211,26 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Hår, päls, fjäll eller fjädrar</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Hair, fur, scale or feather</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124191655</v>
+        <v>124188895</v>
       </c>
       <c r="B25" t="n">
-        <v>56722</v>
+        <v>57942</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3224,43 +3239,43 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100138</v>
+        <v>103001</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Tjäder , Mpd</t>
+          <t>Rödvingetrast, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>595903</v>
+        <v>595997</v>
       </c>
       <c r="R25" t="n">
-        <v>6928353</v>
+        <v>6928324</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3290,19 +3305,9 @@
           <t>2025-04-18</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>11:40</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-04-18</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>11:40</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3317,22 +3322,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124191705</v>
+        <v>124201656</v>
       </c>
       <c r="B26" t="n">
-        <v>57666</v>
+        <v>56714</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3345,34 +3350,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103021</v>
+        <v>102612</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Talltita , Mpd</t>
+          <t>Järpebajs, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>595923</v>
+        <v>596201</v>
       </c>
       <c r="R26" t="n">
-        <v>6928341</v>
+        <v>6928367</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3402,26 +3407,11 @@
           <t>2025-04-18</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>11:42</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-04-18</t>
         </is>
       </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>11:42</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>2 talltita kan höras i träden</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3430,16 +3420,26 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>Spillning</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Dropping</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>

--- a/artfynd/A 21662-2022 artfynd.xlsx
+++ b/artfynd/A 21662-2022 artfynd.xlsx
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124128891</v>
+        <v>124120714</v>
       </c>
       <c r="B7" t="n">
-        <v>79891</v>
+        <v>57529</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1251,37 +1251,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lunglav, Mpd</t>
+          <t>Spillkråka, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>596126</v>
+        <v>595866</v>
       </c>
       <c r="R7" t="n">
-        <v>6928361</v>
+        <v>6928388</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1337,10 +1342,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124120714</v>
+        <v>124128891</v>
       </c>
       <c r="B8" t="n">
-        <v>57529</v>
+        <v>79891</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1353,42 +1358,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Spillkråka, Mpd</t>
+          <t>Lunglav, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>595866</v>
+        <v>596126</v>
       </c>
       <c r="R8" t="n">
-        <v>6928388</v>
+        <v>6928361</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1444,10 +1444,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124186575</v>
+        <v>124193338</v>
       </c>
       <c r="B9" t="n">
-        <v>79891</v>
+        <v>56722</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1456,38 +1456,43 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Lynglav, Mpd</t>
+          <t>Tjäder , Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>596036</v>
+        <v>595945</v>
       </c>
       <c r="R9" t="n">
-        <v>6928364</v>
+        <v>6928357</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1517,9 +1522,19 @@
           <t>2025-04-18</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-04-18</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1534,19 +1549,19 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124198508</v>
+        <v>124192837</v>
       </c>
       <c r="B10" t="n">
         <v>56722</v>
@@ -1580,26 +1595,16 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Tjäderfjäder, Mpd</t>
+          <t>Talltita , Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>596067</v>
+        <v>595923</v>
       </c>
       <c r="R10" t="n">
-        <v>6928345</v>
+        <v>6928341</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1629,11 +1634,21 @@
           <t>2025-04-18</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-04-18</t>
         </is>
       </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1642,36 +1657,26 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Hår, päls, fjäll eller fjädrar</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Hair, fur, scale or feather</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124199083</v>
+        <v>124198508</v>
       </c>
       <c r="B11" t="n">
-        <v>57883</v>
+        <v>56722</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1684,39 +1689,44 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103015</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>hane</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Kungsfågel, Mpd</t>
+          <t>Tjäderfjäder, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>596036</v>
+        <v>596067</v>
       </c>
       <c r="R11" t="n">
-        <v>6928364</v>
+        <v>6928345</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1759,6 +1769,16 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Hår, päls, fjäll eller fjädrar</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Hair, fur, scale or feather</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1887,10 +1907,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124193338</v>
+        <v>124201987</v>
       </c>
       <c r="B13" t="n">
-        <v>56722</v>
+        <v>91012</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1899,43 +1919,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100138</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Tjäder , Mpd</t>
+          <t>Ullticka, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>595945</v>
+        <v>596125</v>
       </c>
       <c r="R13" t="n">
-        <v>6928357</v>
+        <v>6928376</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1965,19 +1980,9 @@
           <t>2025-04-18</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>12:07</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-04-18</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>12:07</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1992,22 +1997,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124191655</v>
+        <v>124201216</v>
       </c>
       <c r="B14" t="n">
-        <v>56722</v>
+        <v>56714</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2016,25 +2021,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100138</v>
+        <v>102612</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2045,14 +2050,14 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Tjäder , Mpd</t>
+          <t>Järpe , Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>595903</v>
+        <v>596199</v>
       </c>
       <c r="R14" t="n">
-        <v>6928353</v>
+        <v>6928355</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2084,7 +2089,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2094,7 +2099,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2121,10 +2126,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124201987</v>
+        <v>124193487</v>
       </c>
       <c r="B15" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2133,38 +2138,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Ullticka, Mpd</t>
+          <t>Garnlav , Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>596125</v>
+        <v>595943</v>
       </c>
       <c r="R15" t="n">
-        <v>6928376</v>
+        <v>6928393</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2194,9 +2199,19 @@
           <t>2025-04-18</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-04-18</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2211,22 +2226,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124193487</v>
+        <v>124188895</v>
       </c>
       <c r="B16" t="n">
-        <v>98101</v>
+        <v>57942</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2235,38 +2250,43 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>103001</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Garnlav , Mpd</t>
+          <t>Rödvingetrast, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>595943</v>
+        <v>595997</v>
       </c>
       <c r="R16" t="n">
-        <v>6928393</v>
+        <v>6928324</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2296,19 +2316,9 @@
           <t>2025-04-18</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>12:14</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-04-18</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>12:14</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2323,22 +2333,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124192837</v>
+        <v>124199083</v>
       </c>
       <c r="B17" t="n">
-        <v>56722</v>
+        <v>57883</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2351,34 +2361,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100138</v>
+        <v>103015</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Talltita , Mpd</t>
+          <t>Kungsfågel, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>595923</v>
+        <v>596036</v>
       </c>
       <c r="R17" t="n">
-        <v>6928341</v>
+        <v>6928364</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2408,19 +2423,9 @@
           <t>2025-04-18</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>12:01</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-04-18</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>12:01</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2435,22 +2440,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124201216</v>
+        <v>124185899</v>
       </c>
       <c r="B18" t="n">
-        <v>56714</v>
+        <v>90977</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2459,43 +2464,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>102612</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Järpe , Mpd</t>
+          <t>Vedticka, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>596199</v>
+        <v>596036</v>
       </c>
       <c r="R18" t="n">
-        <v>6928355</v>
+        <v>6928364</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2525,19 +2525,9 @@
           <t>2025-04-18</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>14:42</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-04-18</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>14:42</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2552,22 +2542,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124185899</v>
+        <v>124185717</v>
       </c>
       <c r="B19" t="n">
-        <v>90977</v>
+        <v>78811</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2576,38 +2566,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5447</v>
+        <v>230405</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Vedticka, Mpd</t>
+          <t>Garnlav , Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>596036</v>
+        <v>595943</v>
       </c>
       <c r="R19" t="n">
-        <v>6928364</v>
+        <v>6928393</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2637,9 +2627,19 @@
           <t>2025-04-18</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>09:33</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-04-18</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2654,22 +2654,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124191705</v>
+        <v>124201656</v>
       </c>
       <c r="B20" t="n">
-        <v>57666</v>
+        <v>56714</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2682,34 +2682,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103021</v>
+        <v>102612</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Talltita , Mpd</t>
+          <t>Järpebajs, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>595923</v>
+        <v>596201</v>
       </c>
       <c r="R20" t="n">
-        <v>6928341</v>
+        <v>6928367</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2739,26 +2739,11 @@
           <t>2025-04-18</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>11:42</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-04-18</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>11:42</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>2 talltita kan höras i träden</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -2767,26 +2752,36 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Spillning</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Dropping</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124206962</v>
+        <v>124199280</v>
       </c>
       <c r="B21" t="n">
-        <v>57680</v>
+        <v>57666</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2795,44 +2790,43 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>266237</v>
+        <v>103021</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Talltita x tofsmes</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Poecile montanus x Lophophanes cristatus</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr"/>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Större hackspett , Mpd</t>
+          <t>Talltita, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>596168</v>
+        <v>596095</v>
       </c>
       <c r="R21" t="n">
-        <v>6928357</v>
+        <v>6928397</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2862,19 +2856,9 @@
           <t>2025-04-18</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>16:55</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-04-18</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>16:55</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2889,22 +2873,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124199280</v>
+        <v>124189689</v>
       </c>
       <c r="B22" t="n">
-        <v>57666</v>
+        <v>57948</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2917,39 +2901,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103021</v>
+        <v>102999</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Talltita, Mpd</t>
+          <t>Björktrast, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>596095</v>
+        <v>595952</v>
       </c>
       <c r="R22" t="n">
-        <v>6928397</v>
+        <v>6928371</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3008,10 +2992,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124189689</v>
+        <v>124186575</v>
       </c>
       <c r="B23" t="n">
-        <v>57948</v>
+        <v>79891</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3024,39 +3008,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>102999</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Björktrast, Mpd</t>
+          <t>Lynglav, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>595952</v>
+        <v>596036</v>
       </c>
       <c r="R23" t="n">
-        <v>6928371</v>
+        <v>6928364</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3115,10 +3094,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124185717</v>
+        <v>124191705</v>
       </c>
       <c r="B24" t="n">
-        <v>78811</v>
+        <v>57666</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3131,34 +3110,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>230405</v>
+        <v>103021</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Garnlav , Mpd</t>
+          <t>Talltita , Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>595943</v>
+        <v>595923</v>
       </c>
       <c r="R24" t="n">
-        <v>6928393</v>
+        <v>6928341</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3190,7 +3169,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3200,7 +3179,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>11:42</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>2 talltita kan höras i träden</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3227,10 +3211,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124188895</v>
+        <v>124191655</v>
       </c>
       <c r="B25" t="n">
-        <v>57942</v>
+        <v>56722</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3239,43 +3223,43 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103001</v>
+        <v>100138</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Rödvingetrast, Mpd</t>
+          <t>Tjäder , Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>595997</v>
+        <v>595903</v>
       </c>
       <c r="R25" t="n">
-        <v>6928324</v>
+        <v>6928353</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3305,9 +3289,19 @@
           <t>2025-04-18</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-04-18</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3322,22 +3316,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124201656</v>
+        <v>124206962</v>
       </c>
       <c r="B26" t="n">
-        <v>56714</v>
+        <v>57680</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3346,38 +3340,44 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>102612</v>
+        <v>266237</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Talltita x tofsmes</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Poecile montanus x Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Järpebajs, Mpd</t>
+          <t>Större hackspett , Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>596201</v>
+        <v>596168</v>
       </c>
       <c r="R26" t="n">
-        <v>6928367</v>
+        <v>6928357</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3407,11 +3407,21 @@
           <t>2025-04-18</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-04-18</t>
         </is>
       </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3420,26 +3430,16 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>Spillning</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Dropping</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>

--- a/artfynd/A 21662-2022 artfynd.xlsx
+++ b/artfynd/A 21662-2022 artfynd.xlsx
@@ -1444,10 +1444,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124193338</v>
+        <v>124201656</v>
       </c>
       <c r="B9" t="n">
-        <v>56722</v>
+        <v>56714</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1456,43 +1456,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>102612</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Tjäder , Mpd</t>
+          <t>Järpebajs, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>595945</v>
+        <v>596201</v>
       </c>
       <c r="R9" t="n">
-        <v>6928357</v>
+        <v>6928367</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1522,21 +1517,11 @@
           <t>2025-04-18</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>12:07</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-04-18</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>12:07</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1545,26 +1530,36 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Spillning</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Dropping</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124192837</v>
+        <v>124199280</v>
       </c>
       <c r="B10" t="n">
-        <v>56722</v>
+        <v>57666</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1573,38 +1568,43 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Talltita , Mpd</t>
+          <t>Talltita, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>595923</v>
+        <v>596095</v>
       </c>
       <c r="R10" t="n">
-        <v>6928341</v>
+        <v>6928397</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1634,19 +1634,9 @@
           <t>2025-04-18</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>12:01</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-04-18</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>12:01</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1661,22 +1651,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124198508</v>
+        <v>124206962</v>
       </c>
       <c r="B11" t="n">
-        <v>56722</v>
+        <v>57680</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1689,44 +1679,40 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>266237</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita x tofsmes</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
+          <t>Poecile montanus x Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
           <t>adult</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>hane</t>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Tjäderfjäder, Mpd</t>
+          <t>Större hackspett , Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>596067</v>
+        <v>596168</v>
       </c>
       <c r="R11" t="n">
-        <v>6928345</v>
+        <v>6928357</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1756,11 +1742,21 @@
           <t>2025-04-18</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-04-18</t>
         </is>
       </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1769,36 +1765,26 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Hår, päls, fjäll eller fjädrar</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Hair, fur, scale or feather</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124197321</v>
+        <v>124201987</v>
       </c>
       <c r="B12" t="n">
-        <v>78811</v>
+        <v>91012</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1811,34 +1797,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>230405</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>garnlav , Mpd</t>
+          <t>Ullticka, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>596021</v>
+        <v>596125</v>
       </c>
       <c r="R12" t="n">
-        <v>6928323</v>
+        <v>6928376</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1868,19 +1854,9 @@
           <t>2025-04-18</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>13:18</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-04-18</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>13:18</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1895,22 +1871,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124201987</v>
+        <v>124193338</v>
       </c>
       <c r="B13" t="n">
-        <v>91012</v>
+        <v>56722</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1919,38 +1895,43 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Ullticka, Mpd</t>
+          <t>Tjäder , Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>596125</v>
+        <v>595945</v>
       </c>
       <c r="R13" t="n">
-        <v>6928376</v>
+        <v>6928357</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1980,9 +1961,19 @@
           <t>2025-04-18</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-04-18</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1997,22 +1988,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124201216</v>
+        <v>124189689</v>
       </c>
       <c r="B14" t="n">
-        <v>56714</v>
+        <v>57948</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2025,39 +2016,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102612</v>
+        <v>102999</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Järpe , Mpd</t>
+          <t>Björktrast, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>596199</v>
+        <v>595952</v>
       </c>
       <c r="R14" t="n">
-        <v>6928355</v>
+        <v>6928371</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2087,19 +2078,9 @@
           <t>2025-04-18</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>14:42</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-04-18</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>14:42</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2114,22 +2095,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124193487</v>
+        <v>124185899</v>
       </c>
       <c r="B15" t="n">
-        <v>98101</v>
+        <v>90977</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2138,38 +2119,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Garnlav , Mpd</t>
+          <t>Vedticka, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>595943</v>
+        <v>596036</v>
       </c>
       <c r="R15" t="n">
-        <v>6928393</v>
+        <v>6928364</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2199,19 +2180,9 @@
           <t>2025-04-18</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>12:14</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-04-18</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>12:14</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2226,22 +2197,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124188895</v>
+        <v>124197321</v>
       </c>
       <c r="B16" t="n">
-        <v>57942</v>
+        <v>78811</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2254,39 +2225,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103001</v>
+        <v>230405</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Rödvingetrast, Mpd</t>
+          <t>garnlav , Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>595997</v>
+        <v>596021</v>
       </c>
       <c r="R16" t="n">
-        <v>6928324</v>
+        <v>6928323</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2316,9 +2282,19 @@
           <t>2025-04-18</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>13:18</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-04-18</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2333,22 +2309,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124199083</v>
+        <v>124191655</v>
       </c>
       <c r="B17" t="n">
-        <v>57883</v>
+        <v>56722</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2361,39 +2337,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103015</v>
+        <v>100138</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Kungsfågel, Mpd</t>
+          <t>Tjäder , Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>596036</v>
+        <v>595903</v>
       </c>
       <c r="R17" t="n">
-        <v>6928364</v>
+        <v>6928353</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2423,9 +2399,19 @@
           <t>2025-04-18</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-04-18</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2440,22 +2426,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124185899</v>
+        <v>124198508</v>
       </c>
       <c r="B18" t="n">
-        <v>90977</v>
+        <v>56722</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2468,34 +2454,44 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>100138</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Vedticka, Mpd</t>
+          <t>Tjäderfjäder, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>596036</v>
+        <v>596067</v>
       </c>
       <c r="R18" t="n">
-        <v>6928364</v>
+        <v>6928345</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2538,6 +2534,16 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>Hår, päls, fjäll eller fjädrar</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Hair, fur, scale or feather</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2666,10 +2672,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124201656</v>
+        <v>124199083</v>
       </c>
       <c r="B20" t="n">
-        <v>56714</v>
+        <v>57883</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2678,20 +2684,20 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>102612</v>
+        <v>103015</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2700,16 +2706,21 @@
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Järpebajs, Mpd</t>
+          <t>Kungsfågel, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>596201</v>
+        <v>596036</v>
       </c>
       <c r="R20" t="n">
-        <v>6928367</v>
+        <v>6928364</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2752,16 +2763,6 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>Spillning</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Dropping</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2778,7 +2779,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124199280</v>
+        <v>124191705</v>
       </c>
       <c r="B21" t="n">
         <v>57666</v>
@@ -2812,21 +2813,16 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Talltita, Mpd</t>
+          <t>Talltita , Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>596095</v>
+        <v>595923</v>
       </c>
       <c r="R21" t="n">
-        <v>6928397</v>
+        <v>6928341</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2856,9 +2852,24 @@
           <t>2025-04-18</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>11:42</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-04-18</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>11:42</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>2 talltita kan höras i träden</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2873,22 +2884,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124189689</v>
+        <v>124192837</v>
       </c>
       <c r="B22" t="n">
-        <v>57948</v>
+        <v>56722</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2897,20 +2908,20 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>102999</v>
+        <v>100138</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2919,21 +2930,16 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Björktrast, Mpd</t>
+          <t>Talltita , Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>595952</v>
+        <v>595923</v>
       </c>
       <c r="R22" t="n">
-        <v>6928371</v>
+        <v>6928341</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2963,9 +2969,19 @@
           <t>2025-04-18</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-04-18</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2980,12 +2996,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -3094,10 +3110,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124191705</v>
+        <v>124193487</v>
       </c>
       <c r="B24" t="n">
-        <v>57666</v>
+        <v>98101</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3106,38 +3122,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Talltita , Mpd</t>
+          <t>Garnlav , Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>595923</v>
+        <v>595943</v>
       </c>
       <c r="R24" t="n">
-        <v>6928341</v>
+        <v>6928393</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3169,7 +3185,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3179,12 +3195,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:42</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>2 talltita kan höras i träden</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3211,10 +3222,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124191655</v>
+        <v>124201216</v>
       </c>
       <c r="B25" t="n">
-        <v>56722</v>
+        <v>56714</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3223,25 +3234,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100138</v>
+        <v>102612</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3252,14 +3263,14 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Tjäder , Mpd</t>
+          <t>Järpe , Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>595903</v>
+        <v>596199</v>
       </c>
       <c r="R25" t="n">
-        <v>6928353</v>
+        <v>6928355</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3291,7 +3302,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3301,7 +3312,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3328,10 +3339,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124206962</v>
+        <v>124188895</v>
       </c>
       <c r="B26" t="n">
-        <v>57680</v>
+        <v>57942</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3340,29 +3351,28 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>266237</v>
+        <v>103001</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Talltita x tofsmes</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Poecile montanus x Lophophanes cristatus</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr"/>
+          <t>Turdus iliacus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
       <c r="M26" t="inlineStr">
         <is>
           <t>spel/sång</t>
@@ -3370,14 +3380,14 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Större hackspett , Mpd</t>
+          <t>Rödvingetrast, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>596168</v>
+        <v>595997</v>
       </c>
       <c r="R26" t="n">
-        <v>6928357</v>
+        <v>6928324</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3407,19 +3417,9 @@
           <t>2025-04-18</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>16:55</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-04-18</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>16:55</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3434,12 +3434,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>

--- a/artfynd/A 21662-2022 artfynd.xlsx
+++ b/artfynd/A 21662-2022 artfynd.xlsx
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124120714</v>
+        <v>124128891</v>
       </c>
       <c r="B7" t="n">
-        <v>57529</v>
+        <v>79891</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1251,42 +1251,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Spillkråka, Mpd</t>
+          <t>Lunglav, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>595866</v>
+        <v>596126</v>
       </c>
       <c r="R7" t="n">
-        <v>6928388</v>
+        <v>6928361</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1342,10 +1337,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124128891</v>
+        <v>124120714</v>
       </c>
       <c r="B8" t="n">
-        <v>79891</v>
+        <v>57529</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1358,37 +1353,42 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lunglav, Mpd</t>
+          <t>Spillkråka, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>596126</v>
+        <v>595866</v>
       </c>
       <c r="R8" t="n">
-        <v>6928361</v>
+        <v>6928388</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1444,10 +1444,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124201656</v>
+        <v>124186575</v>
       </c>
       <c r="B9" t="n">
-        <v>56714</v>
+        <v>79891</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1460,34 +1460,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102612</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Järpebajs, Mpd</t>
+          <t>Lynglav, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>596201</v>
+        <v>596036</v>
       </c>
       <c r="R9" t="n">
-        <v>6928367</v>
+        <v>6928364</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1530,16 +1530,6 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Spillning</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Dropping</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1556,10 +1546,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124199280</v>
+        <v>124193338</v>
       </c>
       <c r="B10" t="n">
-        <v>57666</v>
+        <v>56722</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1568,43 +1558,43 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Talltita, Mpd</t>
+          <t>Tjäder , Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>596095</v>
+        <v>595945</v>
       </c>
       <c r="R10" t="n">
-        <v>6928397</v>
+        <v>6928357</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1634,9 +1624,19 @@
           <t>2025-04-18</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-04-18</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1651,22 +1651,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124206962</v>
+        <v>124191655</v>
       </c>
       <c r="B11" t="n">
-        <v>57680</v>
+        <v>56722</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1679,40 +1679,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>266237</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita x tofsmes</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus x Lophophanes cristatus</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr"/>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Större hackspett , Mpd</t>
+          <t>Tjäder , Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>596168</v>
+        <v>595903</v>
       </c>
       <c r="R11" t="n">
-        <v>6928357</v>
+        <v>6928353</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1744,7 +1743,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1754,7 +1753,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1781,10 +1780,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124201987</v>
+        <v>124193487</v>
       </c>
       <c r="B12" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1793,38 +1792,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Ullticka, Mpd</t>
+          <t>Garnlav , Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>596125</v>
+        <v>595943</v>
       </c>
       <c r="R12" t="n">
-        <v>6928376</v>
+        <v>6928393</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1854,9 +1853,19 @@
           <t>2025-04-18</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-04-18</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1871,22 +1880,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124193338</v>
+        <v>124197321</v>
       </c>
       <c r="B13" t="n">
-        <v>56722</v>
+        <v>78811</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1895,43 +1904,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100138</v>
+        <v>230405</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Tjäder , Mpd</t>
+          <t>garnlav , Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>595945</v>
+        <v>596021</v>
       </c>
       <c r="R13" t="n">
-        <v>6928357</v>
+        <v>6928323</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1963,7 +1967,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1973,7 +1977,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2000,10 +2004,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124189689</v>
+        <v>124199083</v>
       </c>
       <c r="B14" t="n">
-        <v>57948</v>
+        <v>57883</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2012,43 +2016,43 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102999</v>
+        <v>103015</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Björktrast, Mpd</t>
+          <t>Kungsfågel, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>595952</v>
+        <v>596036</v>
       </c>
       <c r="R14" t="n">
-        <v>6928371</v>
+        <v>6928364</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2209,10 +2213,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124197321</v>
+        <v>124192837</v>
       </c>
       <c r="B16" t="n">
-        <v>78811</v>
+        <v>56722</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2221,38 +2225,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>230405</v>
+        <v>100138</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>garnlav , Mpd</t>
+          <t>Talltita , Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>596021</v>
+        <v>595923</v>
       </c>
       <c r="R16" t="n">
-        <v>6928323</v>
+        <v>6928341</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2284,7 +2288,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2294,7 +2298,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2321,10 +2325,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124191655</v>
+        <v>124201987</v>
       </c>
       <c r="B17" t="n">
-        <v>56722</v>
+        <v>91012</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2333,43 +2337,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100138</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Tjäder , Mpd</t>
+          <t>Ullticka, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>595903</v>
+        <v>596125</v>
       </c>
       <c r="R17" t="n">
-        <v>6928353</v>
+        <v>6928376</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2399,19 +2398,9 @@
           <t>2025-04-18</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>11:40</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-04-18</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>11:40</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2426,12 +2415,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2560,10 +2549,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124185717</v>
+        <v>124188895</v>
       </c>
       <c r="B19" t="n">
-        <v>78811</v>
+        <v>57942</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2576,34 +2565,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>230405</v>
+        <v>103001</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Garnlav , Mpd</t>
+          <t>Rödvingetrast, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>595943</v>
+        <v>595997</v>
       </c>
       <c r="R19" t="n">
-        <v>6928393</v>
+        <v>6928324</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2633,19 +2627,9 @@
           <t>2025-04-18</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>09:33</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-04-18</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>09:33</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2660,22 +2644,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124199083</v>
+        <v>124199280</v>
       </c>
       <c r="B20" t="n">
-        <v>57883</v>
+        <v>57666</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2684,43 +2668,43 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Kungsfågel, Mpd</t>
+          <t>Talltita, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>596036</v>
+        <v>596095</v>
       </c>
       <c r="R20" t="n">
-        <v>6928364</v>
+        <v>6928397</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2779,10 +2763,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124191705</v>
+        <v>124206962</v>
       </c>
       <c r="B21" t="n">
-        <v>57666</v>
+        <v>57680</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2791,38 +2775,44 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103021</v>
+        <v>266237</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Talltita x tofsmes</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
+          <t>Poecile montanus x Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Talltita , Mpd</t>
+          <t>Större hackspett , Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>595923</v>
+        <v>596168</v>
       </c>
       <c r="R21" t="n">
-        <v>6928341</v>
+        <v>6928357</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2854,7 +2844,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2864,12 +2854,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:42</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>2 talltita kan höras i träden</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2896,10 +2881,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124192837</v>
+        <v>124201656</v>
       </c>
       <c r="B22" t="n">
-        <v>56722</v>
+        <v>56714</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2908,38 +2893,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100138</v>
+        <v>102612</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Talltita , Mpd</t>
+          <t>Järpebajs, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>595923</v>
+        <v>596201</v>
       </c>
       <c r="R22" t="n">
-        <v>6928341</v>
+        <v>6928367</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2969,21 +2954,11 @@
           <t>2025-04-18</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>12:01</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-04-18</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>12:01</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -2992,26 +2967,36 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Spillning</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Dropping</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124186575</v>
+        <v>124191705</v>
       </c>
       <c r="B23" t="n">
-        <v>79891</v>
+        <v>57666</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3024,34 +3009,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Lynglav, Mpd</t>
+          <t>Talltita , Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>596036</v>
+        <v>595923</v>
       </c>
       <c r="R23" t="n">
-        <v>6928364</v>
+        <v>6928341</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3081,9 +3066,24 @@
           <t>2025-04-18</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>11:42</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-04-18</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>11:42</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>2 talltita kan höras i träden</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3098,22 +3098,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124193487</v>
+        <v>124201216</v>
       </c>
       <c r="B24" t="n">
-        <v>98101</v>
+        <v>56714</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3122,38 +3122,43 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Garnlav , Mpd</t>
+          <t>Järpe , Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>595943</v>
+        <v>596199</v>
       </c>
       <c r="R24" t="n">
-        <v>6928393</v>
+        <v>6928355</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3185,7 +3190,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3195,7 +3200,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3222,10 +3227,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124201216</v>
+        <v>124185717</v>
       </c>
       <c r="B25" t="n">
-        <v>56714</v>
+        <v>78811</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3238,39 +3243,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>102612</v>
+        <v>230405</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Järpe , Mpd</t>
+          <t>Garnlav , Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>596199</v>
+        <v>595943</v>
       </c>
       <c r="R25" t="n">
-        <v>6928355</v>
+        <v>6928393</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3302,7 +3302,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3312,7 +3312,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3339,10 +3339,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124188895</v>
+        <v>124189689</v>
       </c>
       <c r="B26" t="n">
-        <v>57942</v>
+        <v>57948</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3355,39 +3355,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103001</v>
+        <v>102999</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Rödvingetrast, Mpd</t>
+          <t>Björktrast, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>595997</v>
+        <v>595952</v>
       </c>
       <c r="R26" t="n">
-        <v>6928324</v>
+        <v>6928371</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>

--- a/artfynd/A 21662-2022 artfynd.xlsx
+++ b/artfynd/A 21662-2022 artfynd.xlsx
@@ -2656,10 +2656,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124199280</v>
+        <v>124201656</v>
       </c>
       <c r="B20" t="n">
-        <v>57666</v>
+        <v>56714</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2672,39 +2672,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103021</v>
+        <v>102612</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Talltita, Mpd</t>
+          <t>Järpebajs, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>596095</v>
+        <v>596201</v>
       </c>
       <c r="R20" t="n">
-        <v>6928397</v>
+        <v>6928367</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2747,6 +2742,16 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Spillning</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Dropping</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2763,10 +2768,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124206962</v>
+        <v>124199280</v>
       </c>
       <c r="B21" t="n">
-        <v>57680</v>
+        <v>57666</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2775,44 +2780,43 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>266237</v>
+        <v>103021</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Talltita x tofsmes</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Poecile montanus x Lophophanes cristatus</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr"/>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Större hackspett , Mpd</t>
+          <t>Talltita, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>596168</v>
+        <v>596095</v>
       </c>
       <c r="R21" t="n">
-        <v>6928357</v>
+        <v>6928397</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2842,19 +2846,9 @@
           <t>2025-04-18</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>16:55</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-04-18</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>16:55</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2869,22 +2863,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124201656</v>
+        <v>124206962</v>
       </c>
       <c r="B22" t="n">
-        <v>56714</v>
+        <v>57680</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2893,38 +2887,44 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>102612</v>
+        <v>266237</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Talltita x tofsmes</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Poecile montanus x Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Järpebajs, Mpd</t>
+          <t>Större hackspett , Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>596201</v>
+        <v>596168</v>
       </c>
       <c r="R22" t="n">
-        <v>6928367</v>
+        <v>6928357</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2954,11 +2954,21 @@
           <t>2025-04-18</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-04-18</t>
         </is>
       </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -2967,26 +2977,16 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>Spillning</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Dropping</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>

--- a/artfynd/A 21662-2022 artfynd.xlsx
+++ b/artfynd/A 21662-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY30"/>
+  <dimension ref="A1:AY37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124128891</v>
+        <v>124120714</v>
       </c>
       <c r="B7" t="n">
-        <v>79891</v>
+        <v>57529</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1251,37 +1251,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lunglav, Mpd</t>
+          <t>Spillkråka, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>596126</v>
+        <v>595866</v>
       </c>
       <c r="R7" t="n">
-        <v>6928361</v>
+        <v>6928388</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1337,10 +1342,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124120714</v>
+        <v>124128891</v>
       </c>
       <c r="B8" t="n">
-        <v>57529</v>
+        <v>79891</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1353,42 +1358,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Spillkråka, Mpd</t>
+          <t>Lunglav, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>595866</v>
+        <v>596126</v>
       </c>
       <c r="R8" t="n">
-        <v>6928388</v>
+        <v>6928361</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1444,10 +1444,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124186575</v>
+        <v>124185899</v>
       </c>
       <c r="B9" t="n">
-        <v>79891</v>
+        <v>90977</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1456,31 +1456,31 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Lynglav, Mpd</t>
+          <t>Vedticka, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
@@ -1546,10 +1546,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124193338</v>
+        <v>124201216</v>
       </c>
       <c r="B10" t="n">
-        <v>56722</v>
+        <v>56714</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1558,25 +1558,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>102612</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1587,14 +1587,14 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Tjäder , Mpd</t>
+          <t>Järpe , Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>595945</v>
+        <v>596199</v>
       </c>
       <c r="R10" t="n">
-        <v>6928357</v>
+        <v>6928355</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1626,7 +1626,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1636,7 +1636,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1663,10 +1663,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124191655</v>
+        <v>124197321</v>
       </c>
       <c r="B11" t="n">
-        <v>56722</v>
+        <v>78811</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1675,43 +1675,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>230405</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Tjäder , Mpd</t>
+          <t>garnlav , Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>595903</v>
+        <v>596021</v>
       </c>
       <c r="R11" t="n">
-        <v>6928353</v>
+        <v>6928323</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1743,7 +1738,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1753,7 +1748,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1892,10 +1887,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124197321</v>
+        <v>124201656</v>
       </c>
       <c r="B13" t="n">
-        <v>78811</v>
+        <v>56714</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1908,34 +1903,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>230405</v>
+        <v>102612</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>garnlav , Mpd</t>
+          <t>Järpebajs, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>596021</v>
+        <v>596201</v>
       </c>
       <c r="R13" t="n">
-        <v>6928323</v>
+        <v>6928367</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1965,21 +1960,11 @@
           <t>2025-04-18</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>13:18</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-04-18</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>13:18</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -1988,26 +1973,36 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Spillning</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Dropping</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124199083</v>
+        <v>124191705</v>
       </c>
       <c r="B14" t="n">
-        <v>57883</v>
+        <v>57666</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2016,43 +2011,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Kungsfågel, Mpd</t>
+          <t>Talltita , Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>596036</v>
+        <v>595923</v>
       </c>
       <c r="R14" t="n">
-        <v>6928364</v>
+        <v>6928341</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2082,9 +2072,24 @@
           <t>2025-04-18</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>11:42</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-04-18</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>11:42</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>2 talltita kan höras i träden</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2099,22 +2104,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124185899</v>
+        <v>124193338</v>
       </c>
       <c r="B15" t="n">
-        <v>90977</v>
+        <v>56722</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2127,34 +2132,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5447</v>
+        <v>100138</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Vedticka, Mpd</t>
+          <t>Tjäder , Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>596036</v>
+        <v>595945</v>
       </c>
       <c r="R15" t="n">
-        <v>6928364</v>
+        <v>6928357</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2184,9 +2194,19 @@
           <t>2025-04-18</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-04-18</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2201,22 +2221,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124192837</v>
+        <v>124206962</v>
       </c>
       <c r="B16" t="n">
-        <v>56722</v>
+        <v>57680</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2229,34 +2249,40 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100138</v>
+        <v>266237</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita x tofsmes</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
+          <t>Poecile montanus x Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Talltita , Mpd</t>
+          <t>Större hackspett , Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>595923</v>
+        <v>596168</v>
       </c>
       <c r="R16" t="n">
-        <v>6928341</v>
+        <v>6928357</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2288,7 +2314,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2298,7 +2324,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2325,10 +2351,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124201987</v>
+        <v>124186575</v>
       </c>
       <c r="B17" t="n">
-        <v>91012</v>
+        <v>79891</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2341,34 +2367,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Ullticka, Mpd</t>
+          <t>Lynglav, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>596125</v>
+        <v>596036</v>
       </c>
       <c r="R17" t="n">
-        <v>6928376</v>
+        <v>6928364</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2427,10 +2453,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124198508</v>
+        <v>124201987</v>
       </c>
       <c r="B18" t="n">
-        <v>56722</v>
+        <v>91012</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2439,48 +2465,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100138</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Tjäderfjäder, Mpd</t>
+          <t>Ullticka, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>596067</v>
+        <v>596125</v>
       </c>
       <c r="R18" t="n">
-        <v>6928345</v>
+        <v>6928376</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2523,16 +2539,6 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>Hår, päls, fjäll eller fjädrar</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Hair, fur, scale or feather</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2549,10 +2555,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124188895</v>
+        <v>124185717</v>
       </c>
       <c r="B19" t="n">
-        <v>57942</v>
+        <v>78811</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2565,39 +2571,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103001</v>
+        <v>230405</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Rödvingetrast, Mpd</t>
+          <t>Garnlav , Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>595997</v>
+        <v>595943</v>
       </c>
       <c r="R19" t="n">
-        <v>6928324</v>
+        <v>6928393</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2627,9 +2628,19 @@
           <t>2025-04-18</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>09:33</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-04-18</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2644,22 +2655,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124201656</v>
+        <v>124199083</v>
       </c>
       <c r="B20" t="n">
-        <v>56714</v>
+        <v>57883</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2668,20 +2679,20 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>102612</v>
+        <v>103015</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2690,16 +2701,21 @@
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Järpebajs, Mpd</t>
+          <t>Kungsfågel, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>596201</v>
+        <v>596036</v>
       </c>
       <c r="R20" t="n">
-        <v>6928367</v>
+        <v>6928364</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2742,16 +2758,6 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>Spillning</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Dropping</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2875,10 +2881,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124206962</v>
+        <v>124191655</v>
       </c>
       <c r="B22" t="n">
-        <v>57680</v>
+        <v>56722</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2891,40 +2897,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>266237</v>
+        <v>100138</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Talltita x tofsmes</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Poecile montanus x Lophophanes cristatus</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr"/>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Större hackspett , Mpd</t>
+          <t>Tjäder , Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>596168</v>
+        <v>595903</v>
       </c>
       <c r="R22" t="n">
-        <v>6928357</v>
+        <v>6928353</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2956,7 +2961,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2966,7 +2971,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2993,10 +2998,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124191705</v>
+        <v>124192837</v>
       </c>
       <c r="B23" t="n">
-        <v>57666</v>
+        <v>56722</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3005,25 +3010,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3068,7 +3073,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3078,12 +3083,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:42</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>2 talltita kan höras i träden</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3110,10 +3110,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124201216</v>
+        <v>124188895</v>
       </c>
       <c r="B24" t="n">
-        <v>56714</v>
+        <v>57942</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3126,39 +3126,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>102612</v>
+        <v>103001</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Järpe , Mpd</t>
+          <t>Rödvingetrast, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>596199</v>
+        <v>595997</v>
       </c>
       <c r="R24" t="n">
-        <v>6928355</v>
+        <v>6928324</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3188,19 +3188,9 @@
           <t>2025-04-18</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>14:42</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-04-18</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>14:42</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3215,22 +3205,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124185717</v>
+        <v>124189689</v>
       </c>
       <c r="B25" t="n">
-        <v>78811</v>
+        <v>57948</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3243,34 +3233,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>230405</v>
+        <v>102999</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Garnlav , Mpd</t>
+          <t>Björktrast, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>595943</v>
+        <v>595952</v>
       </c>
       <c r="R25" t="n">
-        <v>6928393</v>
+        <v>6928371</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3300,19 +3295,9 @@
           <t>2025-04-18</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>09:33</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-04-18</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>09:33</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3327,22 +3312,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124189689</v>
+        <v>124198508</v>
       </c>
       <c r="B26" t="n">
-        <v>57948</v>
+        <v>56722</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3351,20 +3336,20 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>102999</v>
+        <v>100138</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3373,21 +3358,26 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>hane</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Björktrast, Mpd</t>
+          <t>Tjäderfjäder, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>595952</v>
+        <v>596067</v>
       </c>
       <c r="R26" t="n">
-        <v>6928371</v>
+        <v>6928345</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3430,6 +3420,16 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>Hår, päls, fjäll eller fjädrar</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Hair, fur, scale or feather</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3696,7 +3696,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124246445</v>
+        <v>124246681</v>
       </c>
       <c r="B29" t="n">
         <v>57666</v>
@@ -3739,34 +3739,26 @@
           <t>adult</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+      <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>bobygge</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Talltita x2, Näsvattnet, Sättna, Mpd</t>
+          <t>Talltita, Näsvattnet, Sättna, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>596137</v>
+        <v>596108</v>
       </c>
       <c r="R29" t="n">
-        <v>6928347</v>
+        <v>6928344</v>
       </c>
       <c r="S29" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3800,7 +3792,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Två talltitor bygger ett bo i skogen när jag kommer gåendes är dom först väldigt upprörda och varnar, dom vill ha bort mig där ifrån. Lämnar dom ifred och sätter mig en bit där ifrån då upptar dom bobygget.</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3827,7 +3819,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124246681</v>
+        <v>124246445</v>
       </c>
       <c r="B30" t="n">
         <v>57666</v>
@@ -3870,26 +3862,34 @@
           <t>adult</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr"/>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
+          <t>bobygge</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Talltita, Näsvattnet, Sättna, Mpd</t>
+          <t>Talltita x2, Näsvattnet, Sättna, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>596108</v>
+        <v>596137</v>
       </c>
       <c r="R30" t="n">
-        <v>6928344</v>
+        <v>6928347</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3923,7 +3923,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Två talltitor bygger ett bo i skogen när jag kommer gåendes är dom först väldigt upprörda och varnar, dom vill ha bort mig där ifrån. Lämnar dom ifred och sätter mig en bit där ifrån då upptar dom bobygget.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3947,6 +3947,815 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>124894635</v>
+      </c>
+      <c r="B31" t="n">
+        <v>78810</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Mellantjärn, Mpd</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>596094</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6928363</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Sättna</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-05-09</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>13:37</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-05-09</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>13:37</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>124895163</v>
+      </c>
+      <c r="B32" t="n">
+        <v>79891</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Mellantjärn, Mpd</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>596123</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6928363</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Sättna</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-05-09</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-05-09</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>124895047</v>
+      </c>
+      <c r="B33" t="n">
+        <v>57513</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Mellantjärnen, Mellantjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>596113</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6928348</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Sättna</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-05-09</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-05-09</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>124895718</v>
+      </c>
+      <c r="B34" t="n">
+        <v>57513</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Mellantjärn, Mellantjärn, Mpd</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>596031</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6928336</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Sättna</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-05-09</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-05-09</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>124893384</v>
+      </c>
+      <c r="B35" t="n">
+        <v>79891</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Mellantjärn, Mpd</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>596135</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6928364</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Sättna</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-05-09</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-05-09</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>124896591</v>
+      </c>
+      <c r="B36" t="n">
+        <v>91299</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>658</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Övertjärnen, Övertjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>595901</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6928407</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Sättna</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-05-09</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-05-09</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>124894505</v>
+      </c>
+      <c r="B37" t="n">
+        <v>57529</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Mellantjärn, Mpd</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>596123</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6928363</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Sättna</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-05-09</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>13:37</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-05-09</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>13:37</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 21662-2022 artfynd.xlsx
+++ b/artfynd/A 21662-2022 artfynd.xlsx
@@ -1999,10 +1999,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124191705</v>
+        <v>124193338</v>
       </c>
       <c r="B14" t="n">
-        <v>57666</v>
+        <v>56722</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2011,38 +2011,43 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Talltita , Mpd</t>
+          <t>Tjäder , Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>595923</v>
+        <v>595945</v>
       </c>
       <c r="R14" t="n">
-        <v>6928341</v>
+        <v>6928357</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2074,7 +2079,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2084,12 +2089,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:42</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>2 talltita kan höras i träden</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2116,10 +2116,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124193338</v>
+        <v>124191705</v>
       </c>
       <c r="B15" t="n">
-        <v>56722</v>
+        <v>57666</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2128,43 +2128,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Tjäder , Mpd</t>
+          <t>Talltita , Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>595945</v>
+        <v>595923</v>
       </c>
       <c r="R15" t="n">
-        <v>6928357</v>
+        <v>6928341</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2196,7 +2191,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2206,7 +2201,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:42</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>2 talltita kan höras i träden</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2351,10 +2351,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124186575</v>
+        <v>124201987</v>
       </c>
       <c r="B17" t="n">
-        <v>79891</v>
+        <v>91012</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2367,34 +2367,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Lynglav, Mpd</t>
+          <t>Ullticka, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>596036</v>
+        <v>596125</v>
       </c>
       <c r="R17" t="n">
-        <v>6928364</v>
+        <v>6928376</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2453,10 +2453,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124201987</v>
+        <v>124186575</v>
       </c>
       <c r="B18" t="n">
-        <v>91012</v>
+        <v>79891</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2469,34 +2469,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Ullticka, Mpd</t>
+          <t>Lynglav, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>596125</v>
+        <v>596036</v>
       </c>
       <c r="R18" t="n">
-        <v>6928376</v>
+        <v>6928364</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>

--- a/artfynd/A 21662-2022 artfynd.xlsx
+++ b/artfynd/A 21662-2022 artfynd.xlsx
@@ -1546,10 +1546,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124201216</v>
+        <v>124197321</v>
       </c>
       <c r="B10" t="n">
-        <v>56714</v>
+        <v>78811</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1562,39 +1562,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102612</v>
+        <v>230405</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Järpe , Mpd</t>
+          <t>garnlav , Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>596199</v>
+        <v>596021</v>
       </c>
       <c r="R10" t="n">
-        <v>6928355</v>
+        <v>6928323</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1626,7 +1621,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1636,7 +1631,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1663,10 +1658,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124197321</v>
+        <v>124201216</v>
       </c>
       <c r="B11" t="n">
-        <v>78811</v>
+        <v>56714</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1679,34 +1674,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>230405</v>
+        <v>102612</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>garnlav , Mpd</t>
+          <t>Järpe , Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>596021</v>
+        <v>596199</v>
       </c>
       <c r="R11" t="n">
-        <v>6928323</v>
+        <v>6928355</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1748,7 +1748,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1999,10 +1999,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124193338</v>
+        <v>124191705</v>
       </c>
       <c r="B14" t="n">
-        <v>56722</v>
+        <v>57666</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2011,43 +2011,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Tjäder , Mpd</t>
+          <t>Talltita , Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>595945</v>
+        <v>595923</v>
       </c>
       <c r="R14" t="n">
-        <v>6928357</v>
+        <v>6928341</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2079,7 +2074,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2089,7 +2084,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:42</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>2 talltita kan höras i träden</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2116,10 +2116,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124191705</v>
+        <v>124193338</v>
       </c>
       <c r="B15" t="n">
-        <v>57666</v>
+        <v>56722</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2128,38 +2128,43 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Talltita , Mpd</t>
+          <t>Tjäder , Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>595923</v>
+        <v>595945</v>
       </c>
       <c r="R15" t="n">
-        <v>6928341</v>
+        <v>6928357</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2191,7 +2196,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2201,12 +2206,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:42</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>2 talltita kan höras i träden</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 21662-2022 artfynd.xlsx
+++ b/artfynd/A 21662-2022 artfynd.xlsx
@@ -1444,10 +1444,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124185899</v>
+        <v>124192837</v>
       </c>
       <c r="B9" t="n">
-        <v>90977</v>
+        <v>56722</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1460,34 +1460,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Vedticka, Mpd</t>
+          <t>Talltita , Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>596036</v>
+        <v>595923</v>
       </c>
       <c r="R9" t="n">
-        <v>6928364</v>
+        <v>6928341</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1517,9 +1517,19 @@
           <t>2025-04-18</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-04-18</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1534,22 +1544,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124197321</v>
+        <v>124199083</v>
       </c>
       <c r="B10" t="n">
-        <v>78811</v>
+        <v>57883</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1558,38 +1568,43 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>230405</v>
+        <v>103015</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>garnlav , Mpd</t>
+          <t>Kungsfågel, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>596021</v>
+        <v>596036</v>
       </c>
       <c r="R10" t="n">
-        <v>6928323</v>
+        <v>6928364</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1619,19 +1634,9 @@
           <t>2025-04-18</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>13:18</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-04-18</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>13:18</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1646,22 +1651,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124201216</v>
+        <v>124201987</v>
       </c>
       <c r="B11" t="n">
-        <v>56714</v>
+        <v>91012</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1674,39 +1679,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102612</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Järpe , Mpd</t>
+          <t>Ullticka, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>596199</v>
+        <v>596125</v>
       </c>
       <c r="R11" t="n">
-        <v>6928355</v>
+        <v>6928376</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1736,19 +1736,9 @@
           <t>2025-04-18</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>14:42</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-04-18</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>14:42</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1763,22 +1753,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124193487</v>
+        <v>124198508</v>
       </c>
       <c r="B12" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1787,38 +1777,48 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Garnlav , Mpd</t>
+          <t>Tjäderfjäder, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>595943</v>
+        <v>596067</v>
       </c>
       <c r="R12" t="n">
-        <v>6928393</v>
+        <v>6928345</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1848,21 +1848,11 @@
           <t>2025-04-18</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>12:14</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-04-18</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>12:14</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1871,26 +1861,36 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Hår, päls, fjäll eller fjädrar</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Hair, fur, scale or feather</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124201656</v>
+        <v>124197321</v>
       </c>
       <c r="B13" t="n">
-        <v>56714</v>
+        <v>78811</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1903,34 +1903,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102612</v>
+        <v>230405</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Järpebajs, Mpd</t>
+          <t>garnlav , Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>596201</v>
+        <v>596021</v>
       </c>
       <c r="R13" t="n">
-        <v>6928367</v>
+        <v>6928323</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1960,11 +1960,21 @@
           <t>2025-04-18</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>13:18</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-04-18</t>
         </is>
       </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>13:18</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -1973,36 +1983,26 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Spillning</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Dropping</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124191705</v>
+        <v>124188895</v>
       </c>
       <c r="B14" t="n">
-        <v>57666</v>
+        <v>57942</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2015,34 +2015,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>103001</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Talltita , Mpd</t>
+          <t>Rödvingetrast, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>595923</v>
+        <v>595997</v>
       </c>
       <c r="R14" t="n">
-        <v>6928341</v>
+        <v>6928324</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2072,24 +2077,9 @@
           <t>2025-04-18</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>11:42</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-04-18</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>11:42</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>2 talltita kan höras i träden</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2104,19 +2094,19 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124193338</v>
+        <v>124191655</v>
       </c>
       <c r="B15" t="n">
         <v>56722</v>
@@ -2161,10 +2151,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>595945</v>
+        <v>595903</v>
       </c>
       <c r="R15" t="n">
-        <v>6928357</v>
+        <v>6928353</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2196,7 +2186,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2206,7 +2196,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2233,10 +2223,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124206962</v>
+        <v>124193338</v>
       </c>
       <c r="B16" t="n">
-        <v>57680</v>
+        <v>56722</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2249,37 +2239,36 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>266237</v>
+        <v>100138</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita x tofsmes</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus x Lophophanes cristatus</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Större hackspett , Mpd</t>
+          <t>Tjäder , Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>596168</v>
+        <v>595945</v>
       </c>
       <c r="R16" t="n">
         <v>6928357</v>
@@ -2314,7 +2303,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2324,7 +2313,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2351,10 +2340,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124201987</v>
+        <v>124185899</v>
       </c>
       <c r="B17" t="n">
-        <v>91012</v>
+        <v>90977</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2363,38 +2352,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Ullticka, Mpd</t>
+          <t>Vedticka, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>596125</v>
+        <v>596036</v>
       </c>
       <c r="R17" t="n">
-        <v>6928376</v>
+        <v>6928364</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2453,10 +2442,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124186575</v>
+        <v>124201656</v>
       </c>
       <c r="B18" t="n">
-        <v>79891</v>
+        <v>56714</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2469,34 +2458,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>102612</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Lynglav, Mpd</t>
+          <t>Järpebajs, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>596036</v>
+        <v>596201</v>
       </c>
       <c r="R18" t="n">
-        <v>6928364</v>
+        <v>6928367</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2539,6 +2528,16 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>Spillning</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Dropping</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2555,10 +2554,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124185717</v>
+        <v>124191705</v>
       </c>
       <c r="B19" t="n">
-        <v>78811</v>
+        <v>57666</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2571,34 +2570,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>230405</v>
+        <v>103021</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Garnlav , Mpd</t>
+          <t>Talltita , Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>595943</v>
+        <v>595923</v>
       </c>
       <c r="R19" t="n">
-        <v>6928393</v>
+        <v>6928341</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2630,7 +2629,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2640,7 +2639,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>11:42</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>2 talltita kan höras i träden</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2667,10 +2671,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124199083</v>
+        <v>124199280</v>
       </c>
       <c r="B20" t="n">
-        <v>57883</v>
+        <v>57666</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2679,43 +2683,43 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Kungsfågel, Mpd</t>
+          <t>Talltita, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>596036</v>
+        <v>596095</v>
       </c>
       <c r="R20" t="n">
-        <v>6928364</v>
+        <v>6928397</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2774,10 +2778,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124199280</v>
+        <v>124193487</v>
       </c>
       <c r="B21" t="n">
-        <v>57666</v>
+        <v>98101</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2786,43 +2790,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Talltita, Mpd</t>
+          <t>Garnlav , Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>596095</v>
+        <v>595943</v>
       </c>
       <c r="R21" t="n">
-        <v>6928397</v>
+        <v>6928393</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2852,9 +2851,19 @@
           <t>2025-04-18</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-04-18</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2869,22 +2878,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124191655</v>
+        <v>124206962</v>
       </c>
       <c r="B22" t="n">
-        <v>56722</v>
+        <v>57680</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2897,39 +2906,40 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100138</v>
+        <v>266237</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita x tofsmes</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
+          <t>Poecile montanus x Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Tjäder , Mpd</t>
+          <t>Större hackspett , Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>595903</v>
+        <v>596168</v>
       </c>
       <c r="R22" t="n">
-        <v>6928353</v>
+        <v>6928357</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2961,7 +2971,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2971,7 +2981,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2998,10 +3008,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124192837</v>
+        <v>124186575</v>
       </c>
       <c r="B23" t="n">
-        <v>56722</v>
+        <v>79891</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3010,38 +3020,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Talltita , Mpd</t>
+          <t>Lynglav, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>595923</v>
+        <v>596036</v>
       </c>
       <c r="R23" t="n">
-        <v>6928341</v>
+        <v>6928364</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3071,19 +3081,9 @@
           <t>2025-04-18</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>12:01</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-04-18</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>12:01</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3098,22 +3098,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124188895</v>
+        <v>124189689</v>
       </c>
       <c r="B24" t="n">
-        <v>57942</v>
+        <v>57948</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3126,39 +3126,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103001</v>
+        <v>102999</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Rödvingetrast, Mpd</t>
+          <t>Björktrast, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>595997</v>
+        <v>595952</v>
       </c>
       <c r="R24" t="n">
-        <v>6928324</v>
+        <v>6928371</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3217,10 +3217,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124189689</v>
+        <v>124185717</v>
       </c>
       <c r="B25" t="n">
-        <v>57948</v>
+        <v>78811</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3233,39 +3233,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>102999</v>
+        <v>230405</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Björktrast, Mpd</t>
+          <t>Garnlav , Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>595952</v>
+        <v>595943</v>
       </c>
       <c r="R25" t="n">
-        <v>6928371</v>
+        <v>6928393</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3295,9 +3290,19 @@
           <t>2025-04-18</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>09:33</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-04-18</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3312,22 +3317,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124198508</v>
+        <v>124201216</v>
       </c>
       <c r="B26" t="n">
-        <v>56722</v>
+        <v>56714</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3336,48 +3341,43 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100138</v>
+        <v>102612</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>hane</t>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Tjäderfjäder, Mpd</t>
+          <t>Järpe , Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>596067</v>
+        <v>596199</v>
       </c>
       <c r="R26" t="n">
-        <v>6928345</v>
+        <v>6928355</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3407,11 +3407,21 @@
           <t>2025-04-18</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>14:42</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-04-18</t>
         </is>
       </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>14:42</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3420,26 +3430,16 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>Hår, päls, fjäll eller fjädrar</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Hair, fur, scale or feather</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -3696,7 +3696,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124246681</v>
+        <v>124246445</v>
       </c>
       <c r="B29" t="n">
         <v>57666</v>
@@ -3739,26 +3739,34 @@
           <t>adult</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
+          <t>bobygge</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Talltita, Näsvattnet, Sättna, Mpd</t>
+          <t>Talltita x2, Näsvattnet, Sättna, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>596108</v>
+        <v>596137</v>
       </c>
       <c r="R29" t="n">
-        <v>6928344</v>
+        <v>6928347</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3792,7 +3800,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Två talltitor bygger ett bo i skogen när jag kommer gåendes är dom först väldigt upprörda och varnar, dom vill ha bort mig där ifrån. Lämnar dom ifred och sätter mig en bit där ifrån då upptar dom bobygget.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3819,7 +3827,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124246445</v>
+        <v>124246681</v>
       </c>
       <c r="B30" t="n">
         <v>57666</v>
@@ -3862,34 +3870,26 @@
           <t>adult</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+      <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>bobygge</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Talltita x2, Näsvattnet, Sättna, Mpd</t>
+          <t>Talltita, Näsvattnet, Sättna, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>596137</v>
+        <v>596108</v>
       </c>
       <c r="R30" t="n">
-        <v>6928347</v>
+        <v>6928344</v>
       </c>
       <c r="S30" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3923,7 +3923,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Två talltitor bygger ett bo i skogen när jag kommer gåendes är dom först väldigt upprörda och varnar, dom vill ha bort mig där ifrån. Lämnar dom ifred och sätter mig en bit där ifrån då upptar dom bobygget.</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3950,10 +3950,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124894635</v>
+        <v>124895163</v>
       </c>
       <c r="B31" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3966,21 +3966,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3990,7 +3990,7 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>596094</v>
+        <v>596123</v>
       </c>
       <c r="R31" t="n">
         <v>6928363</v>
@@ -4025,7 +4025,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4062,10 +4062,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124895163</v>
+        <v>124895047</v>
       </c>
       <c r="B32" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4078,34 +4078,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Mellantjärn, Mpd</t>
+          <t>Mellantjärnen, Mellantjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>596123</v>
+        <v>596113</v>
       </c>
       <c r="R32" t="n">
-        <v>6928363</v>
+        <v>6928348</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4137,7 +4142,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4147,7 +4152,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4162,22 +4172,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124895047</v>
+        <v>124894505</v>
       </c>
       <c r="B33" t="n">
-        <v>57513</v>
+        <v>57529</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4190,16 +4200,16 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -4210,19 +4220,19 @@
       <c r="I33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Mellantjärnen, Mellantjärnen, Mpd</t>
+          <t>Mellantjärn, Mpd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>596113</v>
+        <v>596123</v>
       </c>
       <c r="R33" t="n">
-        <v>6928348</v>
+        <v>6928363</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4254,7 +4264,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4264,12 +4274,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:55</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4284,12 +4289,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -4642,10 +4647,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124894505</v>
+        <v>124894635</v>
       </c>
       <c r="B37" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4658,36 +4663,31 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Mellantjärn, Mpd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>596123</v>
+        <v>596094</v>
       </c>
       <c r="R37" t="n">
         <v>6928363</v>

--- a/artfynd/A 21662-2022 artfynd.xlsx
+++ b/artfynd/A 21662-2022 artfynd.xlsx
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124120714</v>
+        <v>124128891</v>
       </c>
       <c r="B7" t="n">
-        <v>57529</v>
+        <v>79891</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1251,42 +1251,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Spillkråka, Mpd</t>
+          <t>Lunglav, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>595866</v>
+        <v>596126</v>
       </c>
       <c r="R7" t="n">
-        <v>6928388</v>
+        <v>6928361</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1342,10 +1337,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124128891</v>
+        <v>124120714</v>
       </c>
       <c r="B8" t="n">
-        <v>79891</v>
+        <v>57529</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1358,37 +1353,42 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lunglav, Mpd</t>
+          <t>Spillkråka, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>596126</v>
+        <v>595866</v>
       </c>
       <c r="R8" t="n">
-        <v>6928361</v>
+        <v>6928388</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1444,10 +1444,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124192837</v>
+        <v>124206962</v>
       </c>
       <c r="B9" t="n">
-        <v>56722</v>
+        <v>57680</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1460,34 +1460,40 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>266237</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita x tofsmes</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
+          <t>Poecile montanus x Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Talltita , Mpd</t>
+          <t>Större hackspett , Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>595923</v>
+        <v>596168</v>
       </c>
       <c r="R9" t="n">
-        <v>6928341</v>
+        <v>6928357</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1519,7 +1525,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1529,7 +1535,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1556,10 +1562,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124199083</v>
+        <v>124189689</v>
       </c>
       <c r="B10" t="n">
-        <v>57883</v>
+        <v>57948</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1568,43 +1574,43 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103015</v>
+        <v>102999</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Kungsfågel, Mpd</t>
+          <t>Björktrast, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>596036</v>
+        <v>595952</v>
       </c>
       <c r="R10" t="n">
-        <v>6928364</v>
+        <v>6928371</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1663,10 +1669,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124201987</v>
+        <v>124201216</v>
       </c>
       <c r="B11" t="n">
-        <v>91012</v>
+        <v>56714</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1679,34 +1685,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>102612</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Ullticka, Mpd</t>
+          <t>Järpe , Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>596125</v>
+        <v>596199</v>
       </c>
       <c r="R11" t="n">
-        <v>6928376</v>
+        <v>6928355</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1736,9 +1747,19 @@
           <t>2025-04-18</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>14:42</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-04-18</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1753,22 +1774,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124198508</v>
+        <v>124201987</v>
       </c>
       <c r="B12" t="n">
-        <v>56722</v>
+        <v>91012</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1777,48 +1798,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100138</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Tjäderfjäder, Mpd</t>
+          <t>Ullticka, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>596067</v>
+        <v>596125</v>
       </c>
       <c r="R12" t="n">
-        <v>6928345</v>
+        <v>6928376</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1861,16 +1872,6 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Hår, päls, fjäll eller fjädrar</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Hair, fur, scale or feather</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1887,10 +1888,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124197321</v>
+        <v>124193338</v>
       </c>
       <c r="B13" t="n">
-        <v>78811</v>
+        <v>56722</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1899,38 +1900,43 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>230405</v>
+        <v>100138</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>garnlav , Mpd</t>
+          <t>Tjäder , Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>596021</v>
+        <v>595945</v>
       </c>
       <c r="R13" t="n">
-        <v>6928323</v>
+        <v>6928357</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1962,7 +1968,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1972,7 +1978,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1999,10 +2005,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124188895</v>
+        <v>124201656</v>
       </c>
       <c r="B14" t="n">
-        <v>57942</v>
+        <v>56714</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2015,39 +2021,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103001</v>
+        <v>102612</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Rödvingetrast, Mpd</t>
+          <t>Järpebajs, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>595997</v>
+        <v>596201</v>
       </c>
       <c r="R14" t="n">
-        <v>6928324</v>
+        <v>6928367</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2090,6 +2091,16 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Spillning</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Dropping</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2106,10 +2117,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124191655</v>
+        <v>124188895</v>
       </c>
       <c r="B15" t="n">
-        <v>56722</v>
+        <v>57942</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2118,43 +2129,43 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100138</v>
+        <v>103001</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Tjäder , Mpd</t>
+          <t>Rödvingetrast, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>595903</v>
+        <v>595997</v>
       </c>
       <c r="R15" t="n">
-        <v>6928353</v>
+        <v>6928324</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2184,19 +2195,9 @@
           <t>2025-04-18</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>11:40</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-04-18</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>11:40</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2211,22 +2212,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124193338</v>
+        <v>124199083</v>
       </c>
       <c r="B16" t="n">
-        <v>56722</v>
+        <v>57883</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2239,39 +2240,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100138</v>
+        <v>103015</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Tjäder , Mpd</t>
+          <t>Kungsfågel, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>595945</v>
+        <v>596036</v>
       </c>
       <c r="R16" t="n">
-        <v>6928357</v>
+        <v>6928364</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2301,19 +2302,9 @@
           <t>2025-04-18</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>12:07</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-04-18</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>12:07</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2328,22 +2319,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124185899</v>
+        <v>124191705</v>
       </c>
       <c r="B17" t="n">
-        <v>90977</v>
+        <v>57666</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2352,38 +2343,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5447</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Vedticka, Mpd</t>
+          <t>Talltita , Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>596036</v>
+        <v>595923</v>
       </c>
       <c r="R17" t="n">
-        <v>6928364</v>
+        <v>6928341</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2413,9 +2404,24 @@
           <t>2025-04-18</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>11:42</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-04-18</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>11:42</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>2 talltita kan höras i träden</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2430,22 +2436,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124201656</v>
+        <v>124193487</v>
       </c>
       <c r="B18" t="n">
-        <v>56714</v>
+        <v>98101</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2454,38 +2460,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Järpebajs, Mpd</t>
+          <t>Garnlav , Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>596201</v>
+        <v>595943</v>
       </c>
       <c r="R18" t="n">
-        <v>6928367</v>
+        <v>6928393</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2515,11 +2521,21 @@
           <t>2025-04-18</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-04-18</t>
         </is>
       </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2528,36 +2544,26 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>Spillning</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Dropping</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124191705</v>
+        <v>124185717</v>
       </c>
       <c r="B19" t="n">
-        <v>57666</v>
+        <v>78811</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2570,34 +2576,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103021</v>
+        <v>230405</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Talltita , Mpd</t>
+          <t>Garnlav , Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>595923</v>
+        <v>595943</v>
       </c>
       <c r="R19" t="n">
-        <v>6928341</v>
+        <v>6928393</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2629,7 +2635,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2639,12 +2645,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:42</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>2 talltita kan höras i träden</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2671,10 +2672,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124199280</v>
+        <v>124191655</v>
       </c>
       <c r="B20" t="n">
-        <v>57666</v>
+        <v>56722</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2683,43 +2684,43 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Talltita, Mpd</t>
+          <t>Tjäder , Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>596095</v>
+        <v>595903</v>
       </c>
       <c r="R20" t="n">
-        <v>6928397</v>
+        <v>6928353</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2749,9 +2750,19 @@
           <t>2025-04-18</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-04-18</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2766,22 +2777,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124193487</v>
+        <v>124198508</v>
       </c>
       <c r="B21" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2790,38 +2801,48 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Garnlav , Mpd</t>
+          <t>Tjäderfjäder, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>595943</v>
+        <v>596067</v>
       </c>
       <c r="R21" t="n">
-        <v>6928393</v>
+        <v>6928345</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2851,21 +2872,11 @@
           <t>2025-04-18</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>12:14</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-04-18</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>12:14</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -2874,26 +2885,36 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Hår, päls, fjäll eller fjädrar</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Hair, fur, scale or feather</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124206962</v>
+        <v>124199280</v>
       </c>
       <c r="B22" t="n">
-        <v>57680</v>
+        <v>57666</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2902,44 +2923,43 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>266237</v>
+        <v>103021</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Talltita x tofsmes</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Poecile montanus x Lophophanes cristatus</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr"/>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Större hackspett , Mpd</t>
+          <t>Talltita, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>596168</v>
+        <v>596095</v>
       </c>
       <c r="R22" t="n">
-        <v>6928357</v>
+        <v>6928397</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2969,19 +2989,9 @@
           <t>2025-04-18</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>16:55</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-04-18</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>16:55</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2996,12 +3006,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -3110,10 +3120,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124189689</v>
+        <v>124192837</v>
       </c>
       <c r="B24" t="n">
-        <v>57948</v>
+        <v>56722</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3122,20 +3132,20 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>102999</v>
+        <v>100138</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3144,21 +3154,16 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Björktrast, Mpd</t>
+          <t>Talltita , Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>595952</v>
+        <v>595923</v>
       </c>
       <c r="R24" t="n">
-        <v>6928371</v>
+        <v>6928341</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3188,9 +3193,19 @@
           <t>2025-04-18</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-04-18</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3205,22 +3220,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124185717</v>
+        <v>124185899</v>
       </c>
       <c r="B25" t="n">
-        <v>78811</v>
+        <v>90977</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3229,38 +3244,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>230405</v>
+        <v>5447</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Garnlav , Mpd</t>
+          <t>Vedticka, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>595943</v>
+        <v>596036</v>
       </c>
       <c r="R25" t="n">
-        <v>6928393</v>
+        <v>6928364</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3290,19 +3305,9 @@
           <t>2025-04-18</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>09:33</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-04-18</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>09:33</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3317,22 +3322,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124201216</v>
+        <v>124197321</v>
       </c>
       <c r="B26" t="n">
-        <v>56714</v>
+        <v>78811</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3345,39 +3350,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>102612</v>
+        <v>230405</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Järpe , Mpd</t>
+          <t>garnlav , Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>596199</v>
+        <v>596021</v>
       </c>
       <c r="R26" t="n">
-        <v>6928355</v>
+        <v>6928323</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3409,7 +3409,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3696,7 +3696,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124246445</v>
+        <v>124246681</v>
       </c>
       <c r="B29" t="n">
         <v>57666</v>
@@ -3739,34 +3739,26 @@
           <t>adult</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+      <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>bobygge</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Talltita x2, Näsvattnet, Sättna, Mpd</t>
+          <t>Talltita, Näsvattnet, Sättna, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>596137</v>
+        <v>596108</v>
       </c>
       <c r="R29" t="n">
-        <v>6928347</v>
+        <v>6928344</v>
       </c>
       <c r="S29" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3800,7 +3792,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Två talltitor bygger ett bo i skogen när jag kommer gåendes är dom först väldigt upprörda och varnar, dom vill ha bort mig där ifrån. Lämnar dom ifred och sätter mig en bit där ifrån då upptar dom bobygget.</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3827,7 +3819,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124246681</v>
+        <v>124246445</v>
       </c>
       <c r="B30" t="n">
         <v>57666</v>
@@ -3870,26 +3862,34 @@
           <t>adult</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr"/>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
+          <t>bobygge</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Talltita, Näsvattnet, Sättna, Mpd</t>
+          <t>Talltita x2, Näsvattnet, Sättna, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>596108</v>
+        <v>596137</v>
       </c>
       <c r="R30" t="n">
-        <v>6928344</v>
+        <v>6928347</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3923,7 +3923,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Två talltitor bygger ett bo i skogen när jag kommer gåendes är dom först väldigt upprörda och varnar, dom vill ha bort mig där ifrån. Lämnar dom ifred och sätter mig en bit där ifrån då upptar dom bobygget.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3950,10 +3950,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124895163</v>
+        <v>124894635</v>
       </c>
       <c r="B31" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3966,21 +3966,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3990,7 +3990,7 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>596123</v>
+        <v>596094</v>
       </c>
       <c r="R31" t="n">
         <v>6928363</v>
@@ -4025,7 +4025,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4062,10 +4062,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124895047</v>
+        <v>124894505</v>
       </c>
       <c r="B32" t="n">
-        <v>57513</v>
+        <v>57529</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4078,16 +4078,16 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -4098,19 +4098,19 @@
       <c r="I32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Mellantjärnen, Mellantjärnen, Mpd</t>
+          <t>Mellantjärn, Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>596113</v>
+        <v>596123</v>
       </c>
       <c r="R32" t="n">
-        <v>6928348</v>
+        <v>6928363</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4142,7 +4142,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4152,12 +4152,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:55</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4172,22 +4167,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124894505</v>
+        <v>124893384</v>
       </c>
       <c r="B33" t="n">
-        <v>57529</v>
+        <v>79891</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4200,39 +4195,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Mellantjärn, Mpd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>596123</v>
+        <v>596135</v>
       </c>
       <c r="R33" t="n">
-        <v>6928363</v>
+        <v>6928364</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4264,7 +4254,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4274,7 +4264,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4289,22 +4279,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124895718</v>
+        <v>124895163</v>
       </c>
       <c r="B34" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4317,39 +4307,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Mellantjärn, Mellantjärn, Mpd</t>
+          <t>Mellantjärn, Mpd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>596031</v>
+        <v>596123</v>
       </c>
       <c r="R34" t="n">
-        <v>6928336</v>
+        <v>6928363</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4381,7 +4366,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4391,12 +4376,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:15</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4423,10 +4403,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124893384</v>
+        <v>124895047</v>
       </c>
       <c r="B35" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4439,34 +4419,39 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Mellantjärn, Mpd</t>
+          <t>Mellantjärnen, Mellantjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>596135</v>
+        <v>596113</v>
       </c>
       <c r="R35" t="n">
-        <v>6928364</v>
+        <v>6928348</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4498,7 +4483,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4508,7 +4493,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4523,12 +4513,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
@@ -4647,10 +4637,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124894635</v>
+        <v>124895718</v>
       </c>
       <c r="B37" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4663,34 +4653,39 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Mellantjärn, Mpd</t>
+          <t>Mellantjärn, Mellantjärn, Mpd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>596094</v>
+        <v>596031</v>
       </c>
       <c r="R37" t="n">
-        <v>6928363</v>
+        <v>6928336</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4722,7 +4717,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4732,7 +4727,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD37" t="b">

--- a/artfynd/A 21662-2022 artfynd.xlsx
+++ b/artfynd/A 21662-2022 artfynd.xlsx
@@ -1444,10 +1444,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124206962</v>
+        <v>124185899</v>
       </c>
       <c r="B9" t="n">
-        <v>57680</v>
+        <v>90977</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1460,40 +1460,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>266237</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita x tofsmes</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus x Lophophanes cristatus</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Större hackspett , Mpd</t>
+          <t>Vedticka, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>596168</v>
+        <v>596036</v>
       </c>
       <c r="R9" t="n">
-        <v>6928357</v>
+        <v>6928364</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,19 +1517,9 @@
           <t>2025-04-18</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>16:55</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-04-18</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>16:55</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1550,22 +1534,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124189689</v>
+        <v>124198508</v>
       </c>
       <c r="B10" t="n">
-        <v>57948</v>
+        <v>56722</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1574,20 +1558,20 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102999</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1596,21 +1580,26 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>hane</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Björktrast, Mpd</t>
+          <t>Tjäderfjäder, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>595952</v>
+        <v>596067</v>
       </c>
       <c r="R10" t="n">
-        <v>6928371</v>
+        <v>6928345</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1653,6 +1642,16 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Hår, päls, fjäll eller fjädrar</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Hair, fur, scale or feather</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1669,10 +1668,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124201216</v>
+        <v>124185717</v>
       </c>
       <c r="B11" t="n">
-        <v>56714</v>
+        <v>78811</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1685,39 +1684,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102612</v>
+        <v>230405</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Järpe , Mpd</t>
+          <t>Garnlav , Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>596199</v>
+        <v>595943</v>
       </c>
       <c r="R11" t="n">
-        <v>6928355</v>
+        <v>6928393</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1749,7 +1743,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1759,7 +1753,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1786,10 +1780,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124201987</v>
+        <v>124192837</v>
       </c>
       <c r="B12" t="n">
-        <v>91012</v>
+        <v>56722</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1798,38 +1792,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Ullticka, Mpd</t>
+          <t>Talltita , Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>596125</v>
+        <v>595923</v>
       </c>
       <c r="R12" t="n">
-        <v>6928376</v>
+        <v>6928341</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1859,9 +1853,19 @@
           <t>2025-04-18</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-04-18</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1876,22 +1880,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124193338</v>
+        <v>124188895</v>
       </c>
       <c r="B13" t="n">
-        <v>56722</v>
+        <v>57942</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1900,43 +1904,43 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100138</v>
+        <v>103001</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Tjäder , Mpd</t>
+          <t>Rödvingetrast, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>595945</v>
+        <v>595997</v>
       </c>
       <c r="R13" t="n">
-        <v>6928357</v>
+        <v>6928324</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1966,19 +1970,9 @@
           <t>2025-04-18</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>12:07</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-04-18</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>12:07</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1993,22 +1987,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124201656</v>
+        <v>124199083</v>
       </c>
       <c r="B14" t="n">
-        <v>56714</v>
+        <v>57883</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2017,20 +2011,20 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102612</v>
+        <v>103015</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2039,16 +2033,21 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Järpebajs, Mpd</t>
+          <t>Kungsfågel, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>596201</v>
+        <v>596036</v>
       </c>
       <c r="R14" t="n">
-        <v>6928367</v>
+        <v>6928364</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2091,16 +2090,6 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>Spillning</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Dropping</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2117,10 +2106,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124188895</v>
+        <v>124199280</v>
       </c>
       <c r="B15" t="n">
-        <v>57942</v>
+        <v>57666</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2133,39 +2122,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103001</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Rödvingetrast, Mpd</t>
+          <t>Talltita, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>595997</v>
+        <v>596095</v>
       </c>
       <c r="R15" t="n">
-        <v>6928324</v>
+        <v>6928397</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2224,10 +2213,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124199083</v>
+        <v>124193487</v>
       </c>
       <c r="B16" t="n">
-        <v>57883</v>
+        <v>98101</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2236,43 +2225,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Kungsfågel, Mpd</t>
+          <t>Garnlav , Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>596036</v>
+        <v>595943</v>
       </c>
       <c r="R16" t="n">
-        <v>6928364</v>
+        <v>6928393</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2302,9 +2286,19 @@
           <t>2025-04-18</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-04-18</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2319,22 +2313,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124191705</v>
+        <v>124197321</v>
       </c>
       <c r="B17" t="n">
-        <v>57666</v>
+        <v>78811</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2347,34 +2341,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103021</v>
+        <v>230405</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Talltita , Mpd</t>
+          <t>garnlav , Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>595923</v>
+        <v>596021</v>
       </c>
       <c r="R17" t="n">
-        <v>6928341</v>
+        <v>6928323</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2406,7 +2400,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2416,12 +2410,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:42</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>2 talltita kan höras i träden</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2448,10 +2437,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124193487</v>
+        <v>124191655</v>
       </c>
       <c r="B18" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2460,38 +2449,43 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Garnlav , Mpd</t>
+          <t>Tjäder , Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>595943</v>
+        <v>595903</v>
       </c>
       <c r="R18" t="n">
-        <v>6928393</v>
+        <v>6928353</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2523,7 +2517,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2533,7 +2527,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2560,10 +2554,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124185717</v>
+        <v>124201656</v>
       </c>
       <c r="B19" t="n">
-        <v>78811</v>
+        <v>56714</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2576,34 +2570,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>230405</v>
+        <v>102612</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Garnlav , Mpd</t>
+          <t>Järpebajs, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>595943</v>
+        <v>596201</v>
       </c>
       <c r="R19" t="n">
-        <v>6928393</v>
+        <v>6928367</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2633,21 +2627,11 @@
           <t>2025-04-18</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>09:33</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-04-18</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>09:33</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2656,26 +2640,36 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Spillning</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Dropping</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124191655</v>
+        <v>124201216</v>
       </c>
       <c r="B20" t="n">
-        <v>56722</v>
+        <v>56714</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2684,25 +2678,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100138</v>
+        <v>102612</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2713,14 +2707,14 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Tjäder , Mpd</t>
+          <t>Järpe , Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>595903</v>
+        <v>596199</v>
       </c>
       <c r="R20" t="n">
-        <v>6928353</v>
+        <v>6928355</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2752,7 +2746,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2762,7 +2756,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2789,10 +2783,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124198508</v>
+        <v>124191705</v>
       </c>
       <c r="B21" t="n">
-        <v>56722</v>
+        <v>57666</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2801,48 +2795,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Tjäderfjäder, Mpd</t>
+          <t>Talltita , Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>596067</v>
+        <v>595923</v>
       </c>
       <c r="R21" t="n">
-        <v>6928345</v>
+        <v>6928341</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2872,11 +2856,26 @@
           <t>2025-04-18</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>11:42</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-04-18</t>
         </is>
       </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>11:42</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>2 talltita kan höras i träden</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -2885,36 +2884,26 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>Hår, päls, fjäll eller fjädrar</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Hair, fur, scale or feather</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124199280</v>
+        <v>124186575</v>
       </c>
       <c r="B22" t="n">
-        <v>57666</v>
+        <v>79891</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2927,39 +2916,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Talltita, Mpd</t>
+          <t>Lynglav, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>596095</v>
+        <v>596036</v>
       </c>
       <c r="R22" t="n">
-        <v>6928397</v>
+        <v>6928364</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3018,10 +3002,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124186575</v>
+        <v>124189689</v>
       </c>
       <c r="B23" t="n">
-        <v>79891</v>
+        <v>57948</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3034,34 +3018,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>102999</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Lynglav, Mpd</t>
+          <t>Björktrast, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>596036</v>
+        <v>595952</v>
       </c>
       <c r="R23" t="n">
-        <v>6928364</v>
+        <v>6928371</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3120,10 +3109,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124192837</v>
+        <v>124206962</v>
       </c>
       <c r="B24" t="n">
-        <v>56722</v>
+        <v>57680</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3136,34 +3125,40 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100138</v>
+        <v>266237</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita x tofsmes</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
+          <t>Poecile montanus x Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Talltita , Mpd</t>
+          <t>Större hackspett , Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>595923</v>
+        <v>596168</v>
       </c>
       <c r="R24" t="n">
-        <v>6928341</v>
+        <v>6928357</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3195,7 +3190,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3205,7 +3200,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3232,10 +3227,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124185899</v>
+        <v>124193338</v>
       </c>
       <c r="B25" t="n">
-        <v>90977</v>
+        <v>56722</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3248,34 +3243,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5447</v>
+        <v>100138</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Vedticka, Mpd</t>
+          <t>Tjäder , Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>596036</v>
+        <v>595945</v>
       </c>
       <c r="R25" t="n">
-        <v>6928364</v>
+        <v>6928357</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3305,9 +3305,19 @@
           <t>2025-04-18</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-04-18</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3322,22 +3332,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124197321</v>
+        <v>124201987</v>
       </c>
       <c r="B26" t="n">
-        <v>78811</v>
+        <v>91012</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3350,34 +3360,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>230405</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>garnlav , Mpd</t>
+          <t>Ullticka, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>596021</v>
+        <v>596125</v>
       </c>
       <c r="R26" t="n">
-        <v>6928323</v>
+        <v>6928376</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3407,19 +3417,9 @@
           <t>2025-04-18</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>13:18</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-04-18</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>13:18</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3434,12 +3434,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -3950,10 +3950,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124894635</v>
+        <v>124895163</v>
       </c>
       <c r="B31" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3966,21 +3966,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3990,7 +3990,7 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>596094</v>
+        <v>596123</v>
       </c>
       <c r="R31" t="n">
         <v>6928363</v>
@@ -4025,7 +4025,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4062,10 +4062,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124894505</v>
+        <v>124896591</v>
       </c>
       <c r="B32" t="n">
-        <v>57529</v>
+        <v>91299</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4078,39 +4078,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Mellantjärn, Mpd</t>
+          <t>Övertjärnen, Övertjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>596123</v>
+        <v>595901</v>
       </c>
       <c r="R32" t="n">
-        <v>6928363</v>
+        <v>6928407</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4142,7 +4137,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4152,7 +4147,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4167,22 +4162,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124893384</v>
+        <v>124894635</v>
       </c>
       <c r="B33" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4195,21 +4190,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4219,10 +4214,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>596135</v>
+        <v>596094</v>
       </c>
       <c r="R33" t="n">
-        <v>6928364</v>
+        <v>6928363</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4254,7 +4249,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4264,7 +4259,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4279,19 +4274,19 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124895163</v>
+        <v>124893384</v>
       </c>
       <c r="B34" t="n">
         <v>79891</v>
@@ -4331,10 +4326,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>596123</v>
+        <v>596135</v>
       </c>
       <c r="R34" t="n">
-        <v>6928363</v>
+        <v>6928364</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4366,7 +4361,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4376,7 +4371,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4391,19 +4386,19 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124895047</v>
+        <v>124895718</v>
       </c>
       <c r="B35" t="n">
         <v>57513</v>
@@ -4439,19 +4434,19 @@
       <c r="I35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Mellantjärnen, Mellantjärnen, Mpd</t>
+          <t>Mellantjärn, Mellantjärn, Mpd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>596113</v>
+        <v>596031</v>
       </c>
       <c r="R35" t="n">
-        <v>6928348</v>
+        <v>6928336</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4483,7 +4478,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4493,12 +4488,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4513,22 +4508,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124896591</v>
+        <v>124894505</v>
       </c>
       <c r="B36" t="n">
-        <v>91299</v>
+        <v>57529</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4541,34 +4536,39 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Övertjärnen, Övertjärnen, Mpd</t>
+          <t>Mellantjärn, Mpd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>595901</v>
+        <v>596123</v>
       </c>
       <c r="R36" t="n">
-        <v>6928407</v>
+        <v>6928363</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4610,7 +4610,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4625,19 +4625,19 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124895718</v>
+        <v>124895047</v>
       </c>
       <c r="B37" t="n">
         <v>57513</v>
@@ -4673,19 +4673,19 @@
       <c r="I37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Mellantjärn, Mellantjärn, Mpd</t>
+          <t>Mellantjärnen, Mellantjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>596031</v>
+        <v>596113</v>
       </c>
       <c r="R37" t="n">
-        <v>6928336</v>
+        <v>6928348</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4717,7 +4717,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4727,12 +4727,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4747,12 +4747,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>

--- a/artfynd/A 21662-2022 artfynd.xlsx
+++ b/artfynd/A 21662-2022 artfynd.xlsx
@@ -1999,10 +1999,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124199083</v>
+        <v>124199280</v>
       </c>
       <c r="B14" t="n">
-        <v>57883</v>
+        <v>57666</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2011,43 +2011,43 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Kungsfågel, Mpd</t>
+          <t>Talltita, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>596036</v>
+        <v>596095</v>
       </c>
       <c r="R14" t="n">
-        <v>6928364</v>
+        <v>6928397</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2106,10 +2106,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124199280</v>
+        <v>124199083</v>
       </c>
       <c r="B15" t="n">
-        <v>57666</v>
+        <v>57883</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2118,43 +2118,43 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Talltita, Mpd</t>
+          <t>Kungsfågel, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>596095</v>
+        <v>596036</v>
       </c>
       <c r="R15" t="n">
-        <v>6928397</v>
+        <v>6928364</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>

--- a/artfynd/A 21662-2022 artfynd.xlsx
+++ b/artfynd/A 21662-2022 artfynd.xlsx
@@ -1444,10 +1444,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124185899</v>
+        <v>124191705</v>
       </c>
       <c r="B9" t="n">
-        <v>90977</v>
+        <v>57666</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1456,38 +1456,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Vedticka, Mpd</t>
+          <t>Talltita , Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>596036</v>
+        <v>595923</v>
       </c>
       <c r="R9" t="n">
-        <v>6928364</v>
+        <v>6928341</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1517,9 +1517,24 @@
           <t>2025-04-18</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>11:42</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-04-18</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>11:42</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>2 talltita kan höras i träden</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1534,22 +1549,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124198508</v>
+        <v>124185899</v>
       </c>
       <c r="B10" t="n">
-        <v>56722</v>
+        <v>90977</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1562,44 +1577,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Tjäderfjäder, Mpd</t>
+          <t>Vedticka, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>596067</v>
+        <v>596036</v>
       </c>
       <c r="R10" t="n">
-        <v>6928345</v>
+        <v>6928364</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1642,16 +1647,6 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Hår, päls, fjäll eller fjädrar</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Hair, fur, scale or feather</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1780,10 +1775,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124192837</v>
+        <v>124201656</v>
       </c>
       <c r="B12" t="n">
-        <v>56722</v>
+        <v>56714</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1792,38 +1787,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100138</v>
+        <v>102612</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Talltita , Mpd</t>
+          <t>Järpebajs, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>595923</v>
+        <v>596201</v>
       </c>
       <c r="R12" t="n">
-        <v>6928341</v>
+        <v>6928367</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1853,21 +1848,11 @@
           <t>2025-04-18</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>12:01</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-04-18</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>12:01</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1876,26 +1861,36 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Spillning</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Dropping</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124188895</v>
+        <v>124201216</v>
       </c>
       <c r="B13" t="n">
-        <v>57942</v>
+        <v>56714</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1908,39 +1903,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103001</v>
+        <v>102612</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Rödvingetrast, Mpd</t>
+          <t>Järpe , Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>595997</v>
+        <v>596199</v>
       </c>
       <c r="R13" t="n">
-        <v>6928324</v>
+        <v>6928355</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1970,9 +1965,19 @@
           <t>2025-04-18</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>14:42</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-04-18</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1987,22 +1992,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124199280</v>
+        <v>124197321</v>
       </c>
       <c r="B14" t="n">
-        <v>57666</v>
+        <v>78811</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2015,39 +2020,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>230405</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Talltita, Mpd</t>
+          <t>garnlav , Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>596095</v>
+        <v>596021</v>
       </c>
       <c r="R14" t="n">
-        <v>6928397</v>
+        <v>6928323</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2077,9 +2077,19 @@
           <t>2025-04-18</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>13:18</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-04-18</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2094,22 +2104,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124199083</v>
+        <v>124188895</v>
       </c>
       <c r="B15" t="n">
-        <v>57883</v>
+        <v>57942</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2118,25 +2128,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103015</v>
+        <v>103001</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2147,14 +2157,14 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Kungsfågel, Mpd</t>
+          <t>Rödvingetrast, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>596036</v>
+        <v>595997</v>
       </c>
       <c r="R15" t="n">
-        <v>6928364</v>
+        <v>6928324</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2213,10 +2223,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124193487</v>
+        <v>124193338</v>
       </c>
       <c r="B16" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2225,38 +2235,43 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Garnlav , Mpd</t>
+          <t>Tjäder , Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>595943</v>
+        <v>595945</v>
       </c>
       <c r="R16" t="n">
-        <v>6928393</v>
+        <v>6928357</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2288,7 +2303,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2298,7 +2313,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2325,10 +2340,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124197321</v>
+        <v>124193487</v>
       </c>
       <c r="B17" t="n">
-        <v>78811</v>
+        <v>98101</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2337,38 +2352,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>230405</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>garnlav , Mpd</t>
+          <t>Garnlav , Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>596021</v>
+        <v>595943</v>
       </c>
       <c r="R17" t="n">
-        <v>6928323</v>
+        <v>6928393</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2400,7 +2415,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2410,7 +2425,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2437,10 +2452,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124191655</v>
+        <v>124189689</v>
       </c>
       <c r="B18" t="n">
-        <v>56722</v>
+        <v>57948</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2449,20 +2464,20 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100138</v>
+        <v>102999</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2473,19 +2488,19 @@
       <c r="I18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Tjäder , Mpd</t>
+          <t>Björktrast, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>595903</v>
+        <v>595952</v>
       </c>
       <c r="R18" t="n">
-        <v>6928353</v>
+        <v>6928371</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2515,19 +2530,9 @@
           <t>2025-04-18</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>11:40</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-04-18</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>11:40</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2542,22 +2547,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124201656</v>
+        <v>124192837</v>
       </c>
       <c r="B19" t="n">
-        <v>56714</v>
+        <v>56722</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2566,38 +2571,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>102612</v>
+        <v>100138</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Järpebajs, Mpd</t>
+          <t>Talltita , Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>596201</v>
+        <v>595923</v>
       </c>
       <c r="R19" t="n">
-        <v>6928367</v>
+        <v>6928341</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2627,11 +2632,21 @@
           <t>2025-04-18</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-04-18</t>
         </is>
       </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2640,36 +2655,26 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>Spillning</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Dropping</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124201216</v>
+        <v>124191655</v>
       </c>
       <c r="B20" t="n">
-        <v>56714</v>
+        <v>56722</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2678,25 +2683,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>102612</v>
+        <v>100138</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2707,14 +2712,14 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Järpe , Mpd</t>
+          <t>Tjäder , Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>596199</v>
+        <v>595903</v>
       </c>
       <c r="R20" t="n">
-        <v>6928355</v>
+        <v>6928353</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2746,7 +2751,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2756,7 +2761,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2783,10 +2788,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124191705</v>
+        <v>124201987</v>
       </c>
       <c r="B21" t="n">
-        <v>57666</v>
+        <v>91012</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2799,34 +2804,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Talltita , Mpd</t>
+          <t>Ullticka, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>595923</v>
+        <v>596125</v>
       </c>
       <c r="R21" t="n">
-        <v>6928341</v>
+        <v>6928376</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2856,24 +2861,9 @@
           <t>2025-04-18</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>11:42</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-04-18</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>11:42</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>2 talltita kan höras i träden</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2888,22 +2878,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124186575</v>
+        <v>124206962</v>
       </c>
       <c r="B22" t="n">
-        <v>79891</v>
+        <v>57680</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2912,38 +2902,44 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>266237</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita x tofsmes</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
+          <t>Poecile montanus x Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Lynglav, Mpd</t>
+          <t>Större hackspett , Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>596036</v>
+        <v>596168</v>
       </c>
       <c r="R22" t="n">
-        <v>6928364</v>
+        <v>6928357</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2973,9 +2969,19 @@
           <t>2025-04-18</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-04-18</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2990,22 +2996,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124189689</v>
+        <v>124198508</v>
       </c>
       <c r="B23" t="n">
-        <v>57948</v>
+        <v>56722</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3014,20 +3020,20 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>102999</v>
+        <v>100138</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3036,21 +3042,26 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>hane</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Björktrast, Mpd</t>
+          <t>Tjäderfjäder, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>595952</v>
+        <v>596067</v>
       </c>
       <c r="R23" t="n">
-        <v>6928371</v>
+        <v>6928345</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3093,6 +3104,16 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Hår, päls, fjäll eller fjädrar</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Hair, fur, scale or feather</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3109,10 +3130,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124206962</v>
+        <v>124199083</v>
       </c>
       <c r="B24" t="n">
-        <v>57680</v>
+        <v>57883</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3125,25 +3146,24 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>266237</v>
+        <v>103015</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Talltita x tofsmes</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Poecile montanus x Lophophanes cristatus</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr"/>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
       <c r="M24" t="inlineStr">
         <is>
           <t>spel/sång</t>
@@ -3151,14 +3171,14 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Större hackspett , Mpd</t>
+          <t>Kungsfågel, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>596168</v>
+        <v>596036</v>
       </c>
       <c r="R24" t="n">
-        <v>6928357</v>
+        <v>6928364</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3188,19 +3208,9 @@
           <t>2025-04-18</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>16:55</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-04-18</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>16:55</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3215,22 +3225,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124193338</v>
+        <v>124199280</v>
       </c>
       <c r="B25" t="n">
-        <v>56722</v>
+        <v>57666</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3239,43 +3249,43 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Tjäder , Mpd</t>
+          <t>Talltita, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>595945</v>
+        <v>596095</v>
       </c>
       <c r="R25" t="n">
-        <v>6928357</v>
+        <v>6928397</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3305,19 +3315,9 @@
           <t>2025-04-18</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>12:07</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-04-18</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>12:07</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3332,22 +3332,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124201987</v>
+        <v>124186575</v>
       </c>
       <c r="B26" t="n">
-        <v>91012</v>
+        <v>79891</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3360,34 +3360,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Ullticka, Mpd</t>
+          <t>Lynglav, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>596125</v>
+        <v>596036</v>
       </c>
       <c r="R26" t="n">
-        <v>6928376</v>
+        <v>6928364</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3696,7 +3696,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124246681</v>
+        <v>124246445</v>
       </c>
       <c r="B29" t="n">
         <v>57666</v>
@@ -3739,26 +3739,34 @@
           <t>adult</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
+          <t>bobygge</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Talltita, Näsvattnet, Sättna, Mpd</t>
+          <t>Talltita x2, Näsvattnet, Sättna, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>596108</v>
+        <v>596137</v>
       </c>
       <c r="R29" t="n">
-        <v>6928344</v>
+        <v>6928347</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3792,7 +3800,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Två talltitor bygger ett bo i skogen när jag kommer gåendes är dom först väldigt upprörda och varnar, dom vill ha bort mig där ifrån. Lämnar dom ifred och sätter mig en bit där ifrån då upptar dom bobygget.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3819,7 +3827,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124246445</v>
+        <v>124246681</v>
       </c>
       <c r="B30" t="n">
         <v>57666</v>
@@ -3862,34 +3870,26 @@
           <t>adult</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+      <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>bobygge</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Talltita x2, Näsvattnet, Sättna, Mpd</t>
+          <t>Talltita, Näsvattnet, Sättna, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>596137</v>
+        <v>596108</v>
       </c>
       <c r="R30" t="n">
-        <v>6928347</v>
+        <v>6928344</v>
       </c>
       <c r="S30" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3923,7 +3923,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Två talltitor bygger ett bo i skogen när jag kommer gåendes är dom först väldigt upprörda och varnar, dom vill ha bort mig där ifrån. Lämnar dom ifred och sätter mig en bit där ifrån då upptar dom bobygget.</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3950,10 +3950,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124895163</v>
+        <v>124895047</v>
       </c>
       <c r="B31" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3966,34 +3966,39 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Mellantjärn, Mpd</t>
+          <t>Mellantjärnen, Mellantjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>596123</v>
+        <v>596113</v>
       </c>
       <c r="R31" t="n">
-        <v>6928363</v>
+        <v>6928348</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4025,7 +4030,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4035,7 +4040,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4050,22 +4060,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124896591</v>
+        <v>124894505</v>
       </c>
       <c r="B32" t="n">
-        <v>91299</v>
+        <v>57529</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4078,34 +4088,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Övertjärnen, Övertjärnen, Mpd</t>
+          <t>Mellantjärn, Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>595901</v>
+        <v>596123</v>
       </c>
       <c r="R32" t="n">
-        <v>6928407</v>
+        <v>6928363</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4137,7 +4152,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4147,7 +4162,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4162,22 +4177,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124894635</v>
+        <v>124896591</v>
       </c>
       <c r="B33" t="n">
-        <v>78810</v>
+        <v>91299</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4190,34 +4205,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Mellantjärn, Mpd</t>
+          <t>Övertjärnen, Övertjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>596094</v>
+        <v>595901</v>
       </c>
       <c r="R33" t="n">
-        <v>6928363</v>
+        <v>6928407</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4249,7 +4264,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4259,7 +4274,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4274,19 +4289,19 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124893384</v>
+        <v>124895163</v>
       </c>
       <c r="B34" t="n">
         <v>79891</v>
@@ -4326,10 +4341,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>596135</v>
+        <v>596123</v>
       </c>
       <c r="R34" t="n">
-        <v>6928364</v>
+        <v>6928363</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4361,7 +4376,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4371,7 +4386,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4386,22 +4401,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124895718</v>
+        <v>124893384</v>
       </c>
       <c r="B35" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4414,39 +4429,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Mellantjärn, Mellantjärn, Mpd</t>
+          <t>Mellantjärn, Mpd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>596031</v>
+        <v>596135</v>
       </c>
       <c r="R35" t="n">
-        <v>6928336</v>
+        <v>6928364</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4478,7 +4488,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4488,12 +4498,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:15</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4508,22 +4513,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124894505</v>
+        <v>124895718</v>
       </c>
       <c r="B36" t="n">
-        <v>57529</v>
+        <v>57513</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4536,16 +4541,16 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -4561,14 +4566,14 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Mellantjärn, Mpd</t>
+          <t>Mellantjärn, Mellantjärn, Mpd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>596123</v>
+        <v>596031</v>
       </c>
       <c r="R36" t="n">
-        <v>6928363</v>
+        <v>6928336</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4600,7 +4605,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4610,7 +4615,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4637,10 +4647,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124895047</v>
+        <v>124894635</v>
       </c>
       <c r="B37" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4653,39 +4663,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Mellantjärnen, Mellantjärnen, Mpd</t>
+          <t>Mellantjärn, Mpd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>596113</v>
+        <v>596094</v>
       </c>
       <c r="R37" t="n">
-        <v>6928348</v>
+        <v>6928363</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4717,7 +4722,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4727,12 +4732,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:55</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4747,12 +4747,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>

--- a/artfynd/A 21662-2022 artfynd.xlsx
+++ b/artfynd/A 21662-2022 artfynd.xlsx
@@ -3696,7 +3696,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124246445</v>
+        <v>124246681</v>
       </c>
       <c r="B29" t="n">
         <v>57666</v>
@@ -3739,34 +3739,26 @@
           <t>adult</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+      <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>bobygge</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Talltita x2, Näsvattnet, Sättna, Mpd</t>
+          <t>Talltita, Näsvattnet, Sättna, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>596137</v>
+        <v>596108</v>
       </c>
       <c r="R29" t="n">
-        <v>6928347</v>
+        <v>6928344</v>
       </c>
       <c r="S29" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3800,7 +3792,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Två talltitor bygger ett bo i skogen när jag kommer gåendes är dom först väldigt upprörda och varnar, dom vill ha bort mig där ifrån. Lämnar dom ifred och sätter mig en bit där ifrån då upptar dom bobygget.</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3827,7 +3819,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124246681</v>
+        <v>124246445</v>
       </c>
       <c r="B30" t="n">
         <v>57666</v>
@@ -3870,26 +3862,34 @@
           <t>adult</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr"/>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
+          <t>bobygge</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Talltita, Näsvattnet, Sättna, Mpd</t>
+          <t>Talltita x2, Näsvattnet, Sättna, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>596108</v>
+        <v>596137</v>
       </c>
       <c r="R30" t="n">
-        <v>6928344</v>
+        <v>6928347</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3923,7 +3923,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Två talltitor bygger ett bo i skogen när jag kommer gåendes är dom först väldigt upprörda och varnar, dom vill ha bort mig där ifrån. Lämnar dom ifred och sätter mig en bit där ifrån då upptar dom bobygget.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3950,10 +3950,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124895047</v>
+        <v>124894505</v>
       </c>
       <c r="B31" t="n">
-        <v>57513</v>
+        <v>57529</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3966,16 +3966,16 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3986,19 +3986,19 @@
       <c r="I31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Mellantjärnen, Mellantjärnen, Mpd</t>
+          <t>Mellantjärn, Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>596113</v>
+        <v>596123</v>
       </c>
       <c r="R31" t="n">
-        <v>6928348</v>
+        <v>6928363</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4030,7 +4030,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4040,12 +4040,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:55</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4060,22 +4055,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124894505</v>
+        <v>124894635</v>
       </c>
       <c r="B32" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4088,36 +4083,31 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Mellantjärn, Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>596123</v>
+        <v>596094</v>
       </c>
       <c r="R32" t="n">
         <v>6928363</v>
@@ -4189,10 +4179,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124896591</v>
+        <v>124895718</v>
       </c>
       <c r="B33" t="n">
-        <v>91299</v>
+        <v>57513</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4205,34 +4195,39 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Övertjärnen, Övertjärnen, Mpd</t>
+          <t>Mellantjärn, Mellantjärn, Mpd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>595901</v>
+        <v>596031</v>
       </c>
       <c r="R33" t="n">
-        <v>6928407</v>
+        <v>6928336</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4264,7 +4259,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4274,7 +4269,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4289,22 +4289,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124895163</v>
+        <v>124896591</v>
       </c>
       <c r="B34" t="n">
-        <v>79891</v>
+        <v>91299</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4317,34 +4317,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Mellantjärn, Mpd</t>
+          <t>Övertjärnen, Övertjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>596123</v>
+        <v>595901</v>
       </c>
       <c r="R34" t="n">
-        <v>6928363</v>
+        <v>6928407</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4376,7 +4376,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4401,19 +4401,19 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124893384</v>
+        <v>124895163</v>
       </c>
       <c r="B35" t="n">
         <v>79891</v>
@@ -4453,10 +4453,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>596135</v>
+        <v>596123</v>
       </c>
       <c r="R35" t="n">
-        <v>6928364</v>
+        <v>6928363</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4488,7 +4488,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4498,7 +4498,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4513,22 +4513,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124895718</v>
+        <v>124893384</v>
       </c>
       <c r="B36" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4541,39 +4541,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Mellantjärn, Mellantjärn, Mpd</t>
+          <t>Mellantjärn, Mpd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>596031</v>
+        <v>596135</v>
       </c>
       <c r="R36" t="n">
-        <v>6928336</v>
+        <v>6928364</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4605,7 +4600,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4615,12 +4610,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:15</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4635,22 +4625,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124894635</v>
+        <v>124895047</v>
       </c>
       <c r="B37" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4663,34 +4653,39 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Mellantjärn, Mpd</t>
+          <t>Mellantjärnen, Mellantjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>596094</v>
+        <v>596113</v>
       </c>
       <c r="R37" t="n">
-        <v>6928363</v>
+        <v>6928348</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4722,7 +4717,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4732,7 +4727,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4747,12 +4747,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>

--- a/artfynd/A 21662-2022 artfynd.xlsx
+++ b/artfynd/A 21662-2022 artfynd.xlsx
@@ -3950,10 +3950,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124894505</v>
+        <v>124894635</v>
       </c>
       <c r="B31" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3966,36 +3966,31 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Mellantjärn, Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>596123</v>
+        <v>596094</v>
       </c>
       <c r="R31" t="n">
         <v>6928363</v>
@@ -4067,10 +4062,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124894635</v>
+        <v>124894505</v>
       </c>
       <c r="B32" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4083,31 +4078,36 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Mellantjärn, Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>596094</v>
+        <v>596123</v>
       </c>
       <c r="R32" t="n">
         <v>6928363</v>

--- a/artfynd/A 21662-2022 artfynd.xlsx
+++ b/artfynd/A 21662-2022 artfynd.xlsx
@@ -4179,10 +4179,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124895718</v>
+        <v>124896591</v>
       </c>
       <c r="B33" t="n">
-        <v>57513</v>
+        <v>91299</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4195,39 +4195,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Mellantjärn, Mellantjärn, Mpd</t>
+          <t>Övertjärnen, Övertjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>596031</v>
+        <v>595901</v>
       </c>
       <c r="R33" t="n">
-        <v>6928336</v>
+        <v>6928407</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4259,7 +4254,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4269,12 +4264,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:15</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4289,22 +4279,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124896591</v>
+        <v>124895163</v>
       </c>
       <c r="B34" t="n">
-        <v>91299</v>
+        <v>79891</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4317,34 +4307,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Övertjärnen, Övertjärnen, Mpd</t>
+          <t>Mellantjärn, Mpd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>595901</v>
+        <v>596123</v>
       </c>
       <c r="R34" t="n">
-        <v>6928407</v>
+        <v>6928363</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4376,7 +4366,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4386,7 +4376,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4401,22 +4391,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124895163</v>
+        <v>124895718</v>
       </c>
       <c r="B35" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4429,34 +4419,39 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Mellantjärn, Mpd</t>
+          <t>Mellantjärn, Mellantjärn, Mpd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>596123</v>
+        <v>596031</v>
       </c>
       <c r="R35" t="n">
-        <v>6928363</v>
+        <v>6928336</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4488,7 +4483,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4498,7 +4493,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD35" t="b">

--- a/artfynd/A 21662-2022 artfynd.xlsx
+++ b/artfynd/A 21662-2022 artfynd.xlsx
@@ -3696,7 +3696,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124246681</v>
+        <v>124246445</v>
       </c>
       <c r="B29" t="n">
         <v>57666</v>
@@ -3739,26 +3739,34 @@
           <t>adult</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
+          <t>bobygge</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Talltita, Näsvattnet, Sättna, Mpd</t>
+          <t>Talltita x2, Näsvattnet, Sättna, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>596108</v>
+        <v>596137</v>
       </c>
       <c r="R29" t="n">
-        <v>6928344</v>
+        <v>6928347</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3792,7 +3800,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Två talltitor bygger ett bo i skogen när jag kommer gåendes är dom först väldigt upprörda och varnar, dom vill ha bort mig där ifrån. Lämnar dom ifred och sätter mig en bit där ifrån då upptar dom bobygget.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3819,7 +3827,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124246445</v>
+        <v>124246681</v>
       </c>
       <c r="B30" t="n">
         <v>57666</v>
@@ -3862,34 +3870,26 @@
           <t>adult</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+      <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>bobygge</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Talltita x2, Näsvattnet, Sättna, Mpd</t>
+          <t>Talltita, Näsvattnet, Sättna, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>596137</v>
+        <v>596108</v>
       </c>
       <c r="R30" t="n">
-        <v>6928347</v>
+        <v>6928344</v>
       </c>
       <c r="S30" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3923,7 +3923,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Två talltitor bygger ett bo i skogen när jag kommer gåendes är dom först väldigt upprörda och varnar, dom vill ha bort mig där ifrån. Lämnar dom ifred och sätter mig en bit där ifrån då upptar dom bobygget.</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3950,10 +3950,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124894635</v>
+        <v>124895047</v>
       </c>
       <c r="B31" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3966,34 +3966,39 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Mellantjärn, Mpd</t>
+          <t>Mellantjärnen, Mellantjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>596094</v>
+        <v>596113</v>
       </c>
       <c r="R31" t="n">
-        <v>6928363</v>
+        <v>6928348</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4025,7 +4030,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4035,7 +4040,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4050,22 +4060,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124894505</v>
+        <v>124896591</v>
       </c>
       <c r="B32" t="n">
-        <v>57529</v>
+        <v>91299</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4078,39 +4088,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Mellantjärn, Mpd</t>
+          <t>Övertjärnen, Övertjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>596123</v>
+        <v>595901</v>
       </c>
       <c r="R32" t="n">
-        <v>6928363</v>
+        <v>6928407</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4142,7 +4147,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4152,7 +4157,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4167,22 +4172,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124896591</v>
+        <v>124895163</v>
       </c>
       <c r="B33" t="n">
-        <v>91299</v>
+        <v>79891</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4195,34 +4200,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Övertjärnen, Övertjärnen, Mpd</t>
+          <t>Mellantjärn, Mpd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>595901</v>
+        <v>596123</v>
       </c>
       <c r="R33" t="n">
-        <v>6928407</v>
+        <v>6928363</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4254,7 +4259,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4264,7 +4269,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4279,22 +4284,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124895163</v>
+        <v>124894505</v>
       </c>
       <c r="B34" t="n">
-        <v>79891</v>
+        <v>57529</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4307,24 +4312,29 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Mellantjärn, Mpd</t>
@@ -4366,7 +4376,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4376,7 +4386,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4637,10 +4647,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124895047</v>
+        <v>124894635</v>
       </c>
       <c r="B37" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4653,39 +4663,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Mellantjärnen, Mellantjärnen, Mpd</t>
+          <t>Mellantjärn, Mpd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>596113</v>
+        <v>596094</v>
       </c>
       <c r="R37" t="n">
-        <v>6928348</v>
+        <v>6928363</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4717,7 +4722,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4727,12 +4732,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:55</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4747,12 +4747,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>

--- a/artfynd/A 21662-2022 artfynd.xlsx
+++ b/artfynd/A 21662-2022 artfynd.xlsx
@@ -3950,7 +3950,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124895047</v>
+        <v>124895718</v>
       </c>
       <c r="B31" t="n">
         <v>57513</v>
@@ -3986,19 +3986,19 @@
       <c r="I31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Mellantjärnen, Mellantjärnen, Mpd</t>
+          <t>Mellantjärn, Mellantjärn, Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>596113</v>
+        <v>596031</v>
       </c>
       <c r="R31" t="n">
-        <v>6928348</v>
+        <v>6928336</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4030,7 +4030,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4040,12 +4040,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4060,22 +4060,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124896591</v>
+        <v>124893384</v>
       </c>
       <c r="B32" t="n">
-        <v>91299</v>
+        <v>79891</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4088,34 +4088,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Övertjärnen, Övertjärnen, Mpd</t>
+          <t>Mellantjärn, Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>595901</v>
+        <v>596135</v>
       </c>
       <c r="R32" t="n">
-        <v>6928407</v>
+        <v>6928364</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4147,7 +4147,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4157,7 +4157,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4172,12 +4172,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -4296,10 +4296,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124894505</v>
+        <v>124894635</v>
       </c>
       <c r="B34" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4312,36 +4312,31 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Mellantjärn, Mpd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>596123</v>
+        <v>596094</v>
       </c>
       <c r="R34" t="n">
         <v>6928363</v>
@@ -4413,7 +4408,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124895718</v>
+        <v>124895047</v>
       </c>
       <c r="B35" t="n">
         <v>57513</v>
@@ -4449,19 +4444,19 @@
       <c r="I35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Mellantjärn, Mellantjärn, Mpd</t>
+          <t>Mellantjärnen, Mellantjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>596031</v>
+        <v>596113</v>
       </c>
       <c r="R35" t="n">
-        <v>6928336</v>
+        <v>6928348</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4493,7 +4488,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4503,12 +4498,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4523,22 +4518,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124893384</v>
+        <v>124896591</v>
       </c>
       <c r="B36" t="n">
-        <v>79891</v>
+        <v>91299</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4551,34 +4546,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Mellantjärn, Mpd</t>
+          <t>Övertjärnen, Övertjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>596135</v>
+        <v>595901</v>
       </c>
       <c r="R36" t="n">
-        <v>6928364</v>
+        <v>6928407</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4610,7 +4605,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4620,7 +4615,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4635,22 +4630,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124894635</v>
+        <v>124894505</v>
       </c>
       <c r="B37" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4663,31 +4658,36 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Mellantjärn, Mpd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>596094</v>
+        <v>596123</v>
       </c>
       <c r="R37" t="n">
         <v>6928363</v>

--- a/artfynd/A 21662-2022 artfynd.xlsx
+++ b/artfynd/A 21662-2022 artfynd.xlsx
@@ -3950,7 +3950,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124895718</v>
+        <v>124895047</v>
       </c>
       <c r="B31" t="n">
         <v>57513</v>
@@ -3986,19 +3986,19 @@
       <c r="I31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Mellantjärn, Mellantjärn, Mpd</t>
+          <t>Mellantjärnen, Mellantjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>596031</v>
+        <v>596113</v>
       </c>
       <c r="R31" t="n">
-        <v>6928336</v>
+        <v>6928348</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4030,7 +4030,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4040,12 +4040,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4060,22 +4060,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124893384</v>
+        <v>124895718</v>
       </c>
       <c r="B32" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4088,34 +4088,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Mellantjärn, Mpd</t>
+          <t>Mellantjärn, Mellantjärn, Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>596135</v>
+        <v>596031</v>
       </c>
       <c r="R32" t="n">
-        <v>6928364</v>
+        <v>6928336</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4147,7 +4152,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4157,7 +4162,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4172,22 +4182,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124895163</v>
+        <v>124896591</v>
       </c>
       <c r="B33" t="n">
-        <v>79891</v>
+        <v>91299</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4200,34 +4210,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Mellantjärn, Mpd</t>
+          <t>Övertjärnen, Övertjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>596123</v>
+        <v>595901</v>
       </c>
       <c r="R33" t="n">
-        <v>6928363</v>
+        <v>6928407</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4259,7 +4269,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4269,7 +4279,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4284,22 +4294,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124894635</v>
+        <v>124893384</v>
       </c>
       <c r="B34" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4312,21 +4322,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4336,10 +4346,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>596094</v>
+        <v>596135</v>
       </c>
       <c r="R34" t="n">
-        <v>6928363</v>
+        <v>6928364</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4371,7 +4381,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4381,7 +4391,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4396,22 +4406,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124895047</v>
+        <v>124894505</v>
       </c>
       <c r="B35" t="n">
-        <v>57513</v>
+        <v>57529</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4424,16 +4434,16 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -4444,19 +4454,19 @@
       <c r="I35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Mellantjärnen, Mellantjärnen, Mpd</t>
+          <t>Mellantjärn, Mpd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>596113</v>
+        <v>596123</v>
       </c>
       <c r="R35" t="n">
-        <v>6928348</v>
+        <v>6928363</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4488,7 +4498,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4498,12 +4508,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:55</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4518,22 +4523,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124896591</v>
+        <v>124894635</v>
       </c>
       <c r="B36" t="n">
-        <v>91299</v>
+        <v>78810</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4546,34 +4551,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Övertjärnen, Övertjärnen, Mpd</t>
+          <t>Mellantjärn, Mpd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>595901</v>
+        <v>596094</v>
       </c>
       <c r="R36" t="n">
-        <v>6928407</v>
+        <v>6928363</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4605,7 +4610,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4615,7 +4620,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4630,22 +4635,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124894505</v>
+        <v>124895163</v>
       </c>
       <c r="B37" t="n">
-        <v>57529</v>
+        <v>79891</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4658,29 +4663,24 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Mellantjärn, Mpd</t>
@@ -4722,7 +4722,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4732,7 +4732,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD37" t="b">

--- a/artfynd/A 21662-2022 artfynd.xlsx
+++ b/artfynd/A 21662-2022 artfynd.xlsx
@@ -3950,10 +3950,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124895047</v>
+        <v>124894635</v>
       </c>
       <c r="B31" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3966,39 +3966,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Mellantjärnen, Mellantjärnen, Mpd</t>
+          <t>Mellantjärn, Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>596113</v>
+        <v>596094</v>
       </c>
       <c r="R31" t="n">
-        <v>6928348</v>
+        <v>6928363</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4030,7 +4025,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4040,12 +4035,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:55</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4060,19 +4050,19 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124895718</v>
+        <v>124895047</v>
       </c>
       <c r="B32" t="n">
         <v>57513</v>
@@ -4108,19 +4098,19 @@
       <c r="I32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Mellantjärn, Mellantjärn, Mpd</t>
+          <t>Mellantjärnen, Mellantjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>596031</v>
+        <v>596113</v>
       </c>
       <c r="R32" t="n">
-        <v>6928336</v>
+        <v>6928348</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4152,7 +4142,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4162,12 +4152,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4182,22 +4172,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124896591</v>
+        <v>124895718</v>
       </c>
       <c r="B33" t="n">
-        <v>91299</v>
+        <v>57513</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4210,34 +4200,39 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Övertjärnen, Övertjärnen, Mpd</t>
+          <t>Mellantjärn, Mellantjärn, Mpd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>595901</v>
+        <v>596031</v>
       </c>
       <c r="R33" t="n">
-        <v>6928407</v>
+        <v>6928336</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4269,7 +4264,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4279,7 +4274,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4294,22 +4294,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124893384</v>
+        <v>124896591</v>
       </c>
       <c r="B34" t="n">
-        <v>79891</v>
+        <v>91299</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4322,34 +4322,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Mellantjärn, Mpd</t>
+          <t>Övertjärnen, Övertjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>596135</v>
+        <v>595901</v>
       </c>
       <c r="R34" t="n">
-        <v>6928364</v>
+        <v>6928407</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4381,7 +4381,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4391,7 +4391,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4406,22 +4406,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124894505</v>
+        <v>124893384</v>
       </c>
       <c r="B35" t="n">
-        <v>57529</v>
+        <v>79891</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4434,39 +4434,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Mellantjärn, Mpd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>596123</v>
+        <v>596135</v>
       </c>
       <c r="R35" t="n">
-        <v>6928363</v>
+        <v>6928364</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4498,7 +4493,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4508,7 +4503,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4523,22 +4518,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124894635</v>
+        <v>124895163</v>
       </c>
       <c r="B36" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4551,21 +4546,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4575,7 +4570,7 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>596094</v>
+        <v>596123</v>
       </c>
       <c r="R36" t="n">
         <v>6928363</v>
@@ -4610,7 +4605,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4620,7 +4615,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4647,10 +4642,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124895163</v>
+        <v>124894505</v>
       </c>
       <c r="B37" t="n">
-        <v>79891</v>
+        <v>57529</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4663,24 +4658,29 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Mellantjärn, Mpd</t>
@@ -4722,7 +4722,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4732,7 +4732,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD37" t="b">

--- a/artfynd/A 21662-2022 artfynd.xlsx
+++ b/artfynd/A 21662-2022 artfynd.xlsx
@@ -3950,10 +3950,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124894635</v>
+        <v>124896591</v>
       </c>
       <c r="B31" t="n">
-        <v>78810</v>
+        <v>91299</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3966,34 +3966,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Mellantjärn, Mpd</t>
+          <t>Övertjärnen, Övertjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>596094</v>
+        <v>595901</v>
       </c>
       <c r="R31" t="n">
-        <v>6928363</v>
+        <v>6928407</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4025,7 +4025,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4050,22 +4050,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124895047</v>
+        <v>124894635</v>
       </c>
       <c r="B32" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4078,39 +4078,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Mellantjärnen, Mellantjärnen, Mpd</t>
+          <t>Mellantjärn, Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>596113</v>
+        <v>596094</v>
       </c>
       <c r="R32" t="n">
-        <v>6928348</v>
+        <v>6928363</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4142,7 +4137,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4152,12 +4147,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:55</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4172,22 +4162,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124895718</v>
+        <v>124894505</v>
       </c>
       <c r="B33" t="n">
-        <v>57513</v>
+        <v>57529</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4200,16 +4190,16 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -4225,14 +4215,14 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Mellantjärn, Mellantjärn, Mpd</t>
+          <t>Mellantjärn, Mpd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>596031</v>
+        <v>596123</v>
       </c>
       <c r="R33" t="n">
-        <v>6928336</v>
+        <v>6928363</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4264,7 +4254,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4274,12 +4264,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:15</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4306,10 +4291,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124896591</v>
+        <v>124893384</v>
       </c>
       <c r="B34" t="n">
-        <v>91299</v>
+        <v>79891</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4322,34 +4307,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Övertjärnen, Övertjärnen, Mpd</t>
+          <t>Mellantjärn, Mpd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>595901</v>
+        <v>596135</v>
       </c>
       <c r="R34" t="n">
-        <v>6928407</v>
+        <v>6928364</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4381,7 +4366,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4391,7 +4376,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4406,19 +4391,19 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124893384</v>
+        <v>124895163</v>
       </c>
       <c r="B35" t="n">
         <v>79891</v>
@@ -4458,10 +4443,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>596135</v>
+        <v>596123</v>
       </c>
       <c r="R35" t="n">
-        <v>6928364</v>
+        <v>6928363</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4493,7 +4478,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4503,7 +4488,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4518,22 +4503,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124895163</v>
+        <v>124895718</v>
       </c>
       <c r="B36" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4546,34 +4531,39 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Mellantjärn, Mpd</t>
+          <t>Mellantjärn, Mellantjärn, Mpd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>596123</v>
+        <v>596031</v>
       </c>
       <c r="R36" t="n">
-        <v>6928363</v>
+        <v>6928336</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4605,7 +4595,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4615,7 +4605,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4642,10 +4637,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124894505</v>
+        <v>124895047</v>
       </c>
       <c r="B37" t="n">
-        <v>57529</v>
+        <v>57513</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4658,16 +4653,16 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -4678,19 +4673,19 @@
       <c r="I37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Mellantjärn, Mpd</t>
+          <t>Mellantjärnen, Mellantjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>596123</v>
+        <v>596113</v>
       </c>
       <c r="R37" t="n">
-        <v>6928363</v>
+        <v>6928348</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4722,7 +4717,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4732,7 +4727,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4747,12 +4747,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>

--- a/artfynd/A 21662-2022 artfynd.xlsx
+++ b/artfynd/A 21662-2022 artfynd.xlsx
@@ -3950,10 +3950,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124896591</v>
+        <v>124893384</v>
       </c>
       <c r="B31" t="n">
-        <v>91299</v>
+        <v>80028</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3966,34 +3966,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Övertjärnen, Övertjärnen, Mpd</t>
+          <t>Mellantjärn, Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>595901</v>
+        <v>596135</v>
       </c>
       <c r="R31" t="n">
-        <v>6928407</v>
+        <v>6928364</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4025,7 +4025,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4050,22 +4050,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124894635</v>
+        <v>124895718</v>
       </c>
       <c r="B32" t="n">
-        <v>78810</v>
+        <v>57635</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4078,34 +4078,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Mellantjärn, Mpd</t>
+          <t>Mellantjärn, Mellantjärn, Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>596094</v>
+        <v>596031</v>
       </c>
       <c r="R32" t="n">
-        <v>6928363</v>
+        <v>6928336</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4137,7 +4142,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4147,7 +4152,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4174,10 +4184,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124894505</v>
+        <v>124896591</v>
       </c>
       <c r="B33" t="n">
-        <v>57529</v>
+        <v>91459</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4190,39 +4200,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Mellantjärn, Mpd</t>
+          <t>Övertjärnen, Övertjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>596123</v>
+        <v>595901</v>
       </c>
       <c r="R33" t="n">
-        <v>6928363</v>
+        <v>6928407</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4254,7 +4259,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4264,7 +4269,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4279,22 +4284,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124893384</v>
+        <v>124894505</v>
       </c>
       <c r="B34" t="n">
-        <v>79891</v>
+        <v>57632</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4307,34 +4312,39 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Mellantjärn, Mpd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>596135</v>
+        <v>596123</v>
       </c>
       <c r="R34" t="n">
-        <v>6928364</v>
+        <v>6928363</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4366,7 +4376,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4376,7 +4386,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4391,12 +4401,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -4406,7 +4416,7 @@
         <v>124895163</v>
       </c>
       <c r="B35" t="n">
-        <v>79891</v>
+        <v>80028</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4515,10 +4525,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124895718</v>
+        <v>124894635</v>
       </c>
       <c r="B36" t="n">
-        <v>57513</v>
+        <v>78947</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4531,39 +4541,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Mellantjärn, Mellantjärn, Mpd</t>
+          <t>Mellantjärn, Mpd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>596031</v>
+        <v>596094</v>
       </c>
       <c r="R36" t="n">
-        <v>6928336</v>
+        <v>6928363</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4595,7 +4600,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4605,12 +4610,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:15</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4640,7 +4640,7 @@
         <v>124895047</v>
       </c>
       <c r="B37" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>

--- a/artfynd/A 21662-2022 artfynd.xlsx
+++ b/artfynd/A 21662-2022 artfynd.xlsx
@@ -3950,10 +3950,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124893384</v>
+        <v>124894505</v>
       </c>
       <c r="B31" t="n">
-        <v>80028</v>
+        <v>57632</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3966,34 +3966,39 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Mellantjärn, Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>596135</v>
+        <v>596123</v>
       </c>
       <c r="R31" t="n">
-        <v>6928364</v>
+        <v>6928363</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4025,7 +4030,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4035,7 +4040,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4050,22 +4055,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124895718</v>
+        <v>124893384</v>
       </c>
       <c r="B32" t="n">
-        <v>57635</v>
+        <v>80028</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4078,39 +4083,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Mellantjärn, Mellantjärn, Mpd</t>
+          <t>Mellantjärn, Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>596031</v>
+        <v>596135</v>
       </c>
       <c r="R32" t="n">
-        <v>6928336</v>
+        <v>6928364</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4142,7 +4142,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4152,12 +4152,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:15</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4172,22 +4167,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124896591</v>
+        <v>124895718</v>
       </c>
       <c r="B33" t="n">
-        <v>91459</v>
+        <v>57635</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4200,34 +4195,39 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Övertjärnen, Övertjärnen, Mpd</t>
+          <t>Mellantjärn, Mellantjärn, Mpd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>595901</v>
+        <v>596031</v>
       </c>
       <c r="R33" t="n">
-        <v>6928407</v>
+        <v>6928336</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4259,7 +4259,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4269,7 +4269,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4284,22 +4289,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124894505</v>
+        <v>124895163</v>
       </c>
       <c r="B34" t="n">
-        <v>57632</v>
+        <v>80028</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4312,29 +4317,24 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Mellantjärn, Mpd</t>
@@ -4376,7 +4376,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4413,10 +4413,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124895163</v>
+        <v>124895047</v>
       </c>
       <c r="B35" t="n">
-        <v>80028</v>
+        <v>57635</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4429,34 +4429,39 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Mellantjärn, Mpd</t>
+          <t>Mellantjärnen, Mellantjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>596123</v>
+        <v>596113</v>
       </c>
       <c r="R35" t="n">
-        <v>6928363</v>
+        <v>6928348</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4488,7 +4493,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4498,7 +4503,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4513,12 +4523,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
@@ -4637,10 +4647,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124895047</v>
+        <v>124896591</v>
       </c>
       <c r="B37" t="n">
-        <v>57635</v>
+        <v>91459</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4653,39 +4663,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Mellantjärnen, Mellantjärnen, Mpd</t>
+          <t>Övertjärnen, Övertjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>596113</v>
+        <v>595901</v>
       </c>
       <c r="R37" t="n">
-        <v>6928348</v>
+        <v>6928407</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4717,7 +4722,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4727,12 +4732,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:55</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD37" t="b">

--- a/artfynd/A 21662-2022 artfynd.xlsx
+++ b/artfynd/A 21662-2022 artfynd.xlsx
@@ -3955,11 +3955,6 @@
       <c r="B31" t="n">
         <v>57632</v>
       </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D31" t="inlineStr">
         <is>
           <t>NT</t>
@@ -4067,15 +4062,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124893384</v>
+        <v>124894635</v>
       </c>
       <c r="B32" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78947</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4083,21 +4073,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4107,10 +4097,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>596135</v>
+        <v>596094</v>
       </c>
       <c r="R32" t="n">
-        <v>6928364</v>
+        <v>6928363</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4142,7 +4132,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4152,7 +4142,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4167,27 +4157,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124895718</v>
+        <v>124895163</v>
       </c>
       <c r="B33" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80028</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4195,39 +4180,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Mellantjärn, Mellantjärn, Mpd</t>
+          <t>Mellantjärn, Mpd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>596031</v>
+        <v>596123</v>
       </c>
       <c r="R33" t="n">
-        <v>6928336</v>
+        <v>6928363</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4259,7 +4239,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4269,12 +4249,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:15</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4301,15 +4276,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124895163</v>
+        <v>124895718</v>
       </c>
       <c r="B34" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57635</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4317,34 +4287,39 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Mellantjärn, Mpd</t>
+          <t>Mellantjärn, Mellantjärn, Mpd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>596123</v>
+        <v>596031</v>
       </c>
       <c r="R34" t="n">
-        <v>6928363</v>
+        <v>6928336</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4376,7 +4351,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4386,7 +4361,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4413,15 +4393,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124895047</v>
+        <v>124896591</v>
       </c>
       <c r="B35" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91459</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4429,39 +4404,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Mellantjärnen, Mellantjärnen, Mpd</t>
+          <t>Övertjärnen, Övertjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>596113</v>
+        <v>595901</v>
       </c>
       <c r="R35" t="n">
-        <v>6928348</v>
+        <v>6928407</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4493,7 +4463,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4503,12 +4473,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:55</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4535,15 +4500,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124894635</v>
+        <v>124895047</v>
       </c>
       <c r="B36" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57635</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4551,34 +4511,39 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Mellantjärn, Mpd</t>
+          <t>Mellantjärnen, Mellantjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>596094</v>
+        <v>596113</v>
       </c>
       <c r="R36" t="n">
-        <v>6928363</v>
+        <v>6928348</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4610,7 +4575,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4620,7 +4585,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4635,27 +4605,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124896591</v>
+        <v>124893384</v>
       </c>
       <c r="B37" t="n">
-        <v>91459</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80028</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4663,34 +4628,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Övertjärnen, Övertjärnen, Mpd</t>
+          <t>Mellantjärn, Mpd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>595901</v>
+        <v>596135</v>
       </c>
       <c r="R37" t="n">
-        <v>6928407</v>
+        <v>6928364</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4722,7 +4687,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4732,7 +4697,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4747,12 +4712,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>

--- a/artfynd/A 21662-2022 artfynd.xlsx
+++ b/artfynd/A 21662-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY37"/>
+  <dimension ref="A1:AY38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4722,6 +4722,113 @@
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>126626263</v>
+      </c>
+      <c r="B38" t="n">
+        <v>57657</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Spillkråka, Mpd</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>595866</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6928388</v>
+      </c>
+      <c r="S38" t="n">
+        <v>20</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Sättna</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-07-13</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-07-13</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 21662-2022 artfynd.xlsx
+++ b/artfynd/A 21662-2022 artfynd.xlsx
@@ -1340,12 +1340,7 @@
         <v>124120714</v>
       </c>
       <c r="B8" t="n">
-        <v>57529</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57658</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -3572,12 +3567,7 @@
         <v>124247642</v>
       </c>
       <c r="B28" t="n">
-        <v>57529</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57658</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3953,7 +3943,7 @@
         <v>124894505</v>
       </c>
       <c r="B31" t="n">
-        <v>57632</v>
+        <v>57658</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 21662-2022 artfynd.xlsx
+++ b/artfynd/A 21662-2022 artfynd.xlsx
@@ -1340,7 +1340,7 @@
         <v>124120714</v>
       </c>
       <c r="B8" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -3567,7 +3567,7 @@
         <v>124247642</v>
       </c>
       <c r="B28" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3943,7 +3943,7 @@
         <v>124894505</v>
       </c>
       <c r="B31" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 21662-2022 artfynd.xlsx
+++ b/artfynd/A 21662-2022 artfynd.xlsx
@@ -1340,7 +1340,7 @@
         <v>124120714</v>
       </c>
       <c r="B8" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -3567,7 +3567,7 @@
         <v>124247642</v>
       </c>
       <c r="B28" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3943,7 +3943,7 @@
         <v>124894505</v>
       </c>
       <c r="B31" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 21662-2022 artfynd.xlsx
+++ b/artfynd/A 21662-2022 artfynd.xlsx
@@ -1340,7 +1340,7 @@
         <v>124120714</v>
       </c>
       <c r="B8" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -3567,7 +3567,7 @@
         <v>124247642</v>
       </c>
       <c r="B28" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3943,7 +3943,7 @@
         <v>124894505</v>
       </c>
       <c r="B31" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 21662-2022 artfynd.xlsx
+++ b/artfynd/A 21662-2022 artfynd.xlsx
@@ -1340,7 +1340,7 @@
         <v>124120714</v>
       </c>
       <c r="B8" t="n">
-        <v>57669</v>
+        <v>57670</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -3567,7 +3567,7 @@
         <v>124247642</v>
       </c>
       <c r="B28" t="n">
-        <v>57669</v>
+        <v>57670</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3943,7 +3943,7 @@
         <v>124894505</v>
       </c>
       <c r="B31" t="n">
-        <v>57669</v>
+        <v>57670</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 21662-2022 artfynd.xlsx
+++ b/artfynd/A 21662-2022 artfynd.xlsx
@@ -1340,7 +1340,7 @@
         <v>124120714</v>
       </c>
       <c r="B8" t="n">
-        <v>57670</v>
+        <v>57681</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -3567,7 +3567,7 @@
         <v>124247642</v>
       </c>
       <c r="B28" t="n">
-        <v>57670</v>
+        <v>57681</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3943,7 +3943,7 @@
         <v>124894505</v>
       </c>
       <c r="B31" t="n">
-        <v>57670</v>
+        <v>57681</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 21662-2022 artfynd.xlsx
+++ b/artfynd/A 21662-2022 artfynd.xlsx
@@ -4269,7 +4269,7 @@
         <v>124895718</v>
       </c>
       <c r="B34" t="n">
-        <v>57635</v>
+        <v>57736</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4493,7 +4493,7 @@
         <v>124895047</v>
       </c>
       <c r="B36" t="n">
-        <v>57635</v>
+        <v>57736</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4717,7 +4717,7 @@
         <v>126626263</v>
       </c>
       <c r="B38" t="n">
-        <v>57657</v>
+        <v>57736</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 21662-2022 artfynd.xlsx
+++ b/artfynd/A 21662-2022 artfynd.xlsx
@@ -4269,7 +4269,7 @@
         <v>124895718</v>
       </c>
       <c r="B34" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4493,7 +4493,7 @@
         <v>124895047</v>
       </c>
       <c r="B36" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4717,7 +4717,7 @@
         <v>126626263</v>
       </c>
       <c r="B38" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 21662-2022 artfynd.xlsx
+++ b/artfynd/A 21662-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY38"/>
+  <dimension ref="A1:AY53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>105899115</v>
+        <v>105899083</v>
       </c>
       <c r="B2" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>596138.3709686382</v>
+        <v>595973</v>
       </c>
       <c r="R2" t="n">
-        <v>6928345.374976434</v>
+        <v>6928348</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,19 +743,9 @@
           <t>2022-09-14</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-09-14</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,37 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>105899116</v>
+        <v>105899084</v>
       </c>
       <c r="B3" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>596020.3258181214</v>
+        <v>595794</v>
       </c>
       <c r="R3" t="n">
-        <v>6928372.974388107</v>
+        <v>6928408</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -860,19 +840,9 @@
           <t>2022-09-14</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-09-14</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>105899084</v>
+        <v>124896591</v>
       </c>
       <c r="B4" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,37 +880,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>53</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Tjärdalsberget, Mpd</t>
+          <t>Övertjärnen, Övertjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>595793.6248289539</v>
+        <v>595901</v>
       </c>
       <c r="R4" t="n">
-        <v>6928408.093464995</v>
+        <v>6928407</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -969,22 +934,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,27 +964,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Dennis Jonason</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Dennis Jonason</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>105899199</v>
+        <v>124201987</v>
       </c>
       <c r="B5" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,37 +987,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Tjärdalsberget, Mpd</t>
+          <t>Ullticka, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>596064.2618747548</v>
+        <v>596125</v>
       </c>
       <c r="R5" t="n">
-        <v>6928376.092685064</v>
+        <v>6928376</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1081,22 +1041,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-04-18</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-04-18</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1111,27 +1061,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Dennis Jonason</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Dennis Jonason</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>105899083</v>
+        <v>124896614</v>
       </c>
       <c r="B6" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1139,37 +1084,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>53</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Tjärdalsberget, Mpd</t>
+          <t>Övertjärnen, Övertjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>595972.3855790168</v>
+        <v>595899</v>
       </c>
       <c r="R6" t="n">
-        <v>6928347.99121576</v>
+        <v>6928417</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1193,22 +1138,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1223,62 +1168,57 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Dennis Jonason</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Dennis Jonason</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124128891</v>
+        <v>124185899</v>
       </c>
       <c r="B7" t="n">
-        <v>79891</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lunglav, Mpd</t>
+          <t>Vedticka, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>596126</v>
+        <v>596036</v>
       </c>
       <c r="R7" t="n">
-        <v>6928361</v>
+        <v>6928364</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1305,12 +1245,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-04-16</t>
+          <t>2025-04-18</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-04-16</t>
+          <t>2025-04-18</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1337,53 +1277,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124120714</v>
+        <v>105899198</v>
       </c>
       <c r="B8" t="n">
-        <v>57681</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Spillkråka, Mpd</t>
+          <t>Tjärdalsberget, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>595866</v>
+        <v>596199</v>
       </c>
       <c r="R8" t="n">
-        <v>6928388</v>
+        <v>6928385</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1407,12 +1342,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-04-16</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-04-16</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1427,65 +1362,60 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Dennis Jonason</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Dennis Jonason</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124191705</v>
+        <v>105899199</v>
       </c>
       <c r="B9" t="n">
-        <v>57666</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Talltita , Mpd</t>
+          <t>Tjärdalsberget, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>595923</v>
+        <v>596064</v>
       </c>
       <c r="R9" t="n">
-        <v>6928341</v>
+        <v>6928376</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1509,27 +1439,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-04-18</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>11:42</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-04-18</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>11:42</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>2 talltita kan höras i träden</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1544,65 +1459,60 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Dennis Jonason</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Dennis Jonason</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124185899</v>
+        <v>105899200</v>
       </c>
       <c r="B10" t="n">
-        <v>90977</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Vedticka, Mpd</t>
+          <t>Tjärdalsberget, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>596036</v>
+        <v>595783</v>
       </c>
       <c r="R10" t="n">
-        <v>6928364</v>
+        <v>6928416</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1626,12 +1536,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-04-18</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-04-18</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1646,44 +1556,39 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Dennis Jonason</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Dennis Jonason</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124185717</v>
+        <v>124247923</v>
       </c>
       <c r="B11" t="n">
-        <v>78811</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>230405</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1691,17 +1596,24 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Garnlav , Mpd</t>
+          <t>Garnlav 2, Näsvattnet, Sättna, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>595943</v>
+        <v>596214</v>
       </c>
       <c r="R11" t="n">
-        <v>6928393</v>
+        <v>6928390</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1728,22 +1640,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-04-18</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>09:33</t>
+          <t>2025-04-19</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-04-18</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>09:33</t>
+          <t>2025-04-19</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>2 stora garnlav</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1752,6 +1659,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1770,50 +1678,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124201656</v>
+        <v>124894635</v>
       </c>
       <c r="B12" t="n">
-        <v>56714</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Järpebajs, Mpd</t>
+          <t>Mellantjärn, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>596201</v>
+        <v>596094</v>
       </c>
       <c r="R12" t="n">
-        <v>6928367</v>
+        <v>6928363</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1840,12 +1743,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-04-18</t>
+          <t>2025-05-09</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-04-18</t>
+          <t>2025-05-09</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1856,16 +1769,6 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Spillning</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Dropping</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1882,15 +1785,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124201216</v>
+        <v>124128891</v>
       </c>
       <c r="B13" t="n">
-        <v>56714</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1898,39 +1796,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102612</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Järpe , Mpd</t>
+          <t>Lunglav, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>596199</v>
+        <v>596126</v>
       </c>
       <c r="R13" t="n">
-        <v>6928355</v>
+        <v>6928361</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1957,22 +1850,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-04-18</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>14:42</t>
+          <t>2025-04-16</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-04-18</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>14:42</t>
+          <t>2025-04-16</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1987,27 +1870,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124197321</v>
+        <v>124186575</v>
       </c>
       <c r="B14" t="n">
-        <v>78811</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2015,34 +1893,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>230405</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>garnlav , Mpd</t>
+          <t>Lynglav, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>596021</v>
+        <v>596036</v>
       </c>
       <c r="R14" t="n">
-        <v>6928323</v>
+        <v>6928364</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2072,19 +1950,9 @@
           <t>2025-04-18</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>13:18</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-04-18</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>13:18</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2099,27 +1967,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124188895</v>
+        <v>124893384</v>
       </c>
       <c r="B15" t="n">
-        <v>57942</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2127,39 +1990,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103001</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Rödvingetrast, Mpd</t>
+          <t>Mellantjärn, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>595997</v>
+        <v>596135</v>
       </c>
       <c r="R15" t="n">
-        <v>6928324</v>
+        <v>6928364</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2186,12 +2044,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-04-18</t>
+          <t>2025-05-09</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-04-18</t>
+          <t>2025-05-09</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2206,67 +2074,57 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124193338</v>
+        <v>124895163</v>
       </c>
       <c r="B16" t="n">
-        <v>56722</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Tjäder , Mpd</t>
+          <t>Mellantjärn, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>595945</v>
+        <v>596123</v>
       </c>
       <c r="R16" t="n">
-        <v>6928357</v>
+        <v>6928363</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2293,22 +2151,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-04-18</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-04-18</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2323,65 +2181,65 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124193487</v>
+        <v>124120714</v>
       </c>
       <c r="B17" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Garnlav , Mpd</t>
+          <t>Spillkråka, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>595943</v>
+        <v>595866</v>
       </c>
       <c r="R17" t="n">
-        <v>6928393</v>
+        <v>6928388</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2405,22 +2263,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-04-18</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>12:14</t>
+          <t>2025-04-16</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-04-18</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>12:14</t>
+          <t>2025-04-16</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2435,67 +2283,77 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124189689</v>
+        <v>124247642</v>
       </c>
       <c r="B18" t="n">
-        <v>57948</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>102999</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Björktrast, Mpd</t>
+          <t>Spillkråka fjäder, Näsvattnet, Sättna, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>595952</v>
+        <v>595933</v>
       </c>
       <c r="R18" t="n">
-        <v>6928371</v>
+        <v>6928381</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2522,12 +2380,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-04-18</t>
+          <t>2025-04-19</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-04-18</t>
+          <t>2025-04-19</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Tappad blodfjäder av Spillkråka. Spillkråkan har även observerats och hörts inom området vid upprepade olika tillfällen.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2542,27 +2405,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124192837</v>
+        <v>124894505</v>
       </c>
       <c r="B19" t="n">
-        <v>56722</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2570,34 +2428,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Talltita , Mpd</t>
+          <t>Mellantjärn, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>595923</v>
+        <v>596123</v>
       </c>
       <c r="R19" t="n">
-        <v>6928341</v>
+        <v>6928363</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2624,22 +2487,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-04-18</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-04-18</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2654,70 +2517,72 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124191655</v>
+        <v>124138703</v>
       </c>
       <c r="B20" t="n">
-        <v>56722</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
+          <t>bobygge</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Tjäder , Mpd</t>
+          <t>Tretåig hackspett, Näsvattnet, Sättna, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>595903</v>
+        <v>596222</v>
       </c>
       <c r="R20" t="n">
-        <v>6928353</v>
+        <v>6928366</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2741,22 +2606,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-04-18</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>11:40</t>
+          <t>2025-04-16</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-04-18</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>11:40</t>
+          <t>2025-04-16</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett som först satt och trummade för att sedan fortsätta med vad ser ut som ett bobygge. Trummandet fick jag tyvärr inte på videon. Trädet den sitter i är en stor död asp som har fullt av karaktäristiska "hack ringar".</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2771,27 +2631,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124201987</v>
+        <v>124895047</v>
       </c>
       <c r="B21" t="n">
-        <v>91012</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2799,34 +2654,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Ullticka, Mpd</t>
+          <t>Mellantjärnen, Mellantjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>596125</v>
+        <v>596113</v>
       </c>
       <c r="R21" t="n">
-        <v>6928376</v>
+        <v>6928348</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2853,12 +2713,27 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-04-18</t>
+          <t>2025-05-09</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-04-18</t>
+          <t>2025-05-09</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2873,68 +2748,62 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124206962</v>
+        <v>124895718</v>
       </c>
       <c r="B22" t="n">
-        <v>57680</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>266237</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Talltita x tofsmes</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Poecile montanus x Lophophanes cristatus</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Större hackspett , Mpd</t>
+          <t>Mellantjärn, Mellantjärn, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>596168</v>
+        <v>596031</v>
       </c>
       <c r="R22" t="n">
-        <v>6928357</v>
+        <v>6928336</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2961,22 +2830,27 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-04-18</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-04-18</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2991,72 +2865,62 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124198508</v>
+        <v>124895747</v>
       </c>
       <c r="B23" t="n">
-        <v>56722</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>hane</t>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Tjäderfjäder, Mpd</t>
+          <t>Övertjärnen, Övertjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>596067</v>
+        <v>595978</v>
       </c>
       <c r="R23" t="n">
-        <v>6928345</v>
+        <v>6928295</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3083,12 +2947,27 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-04-18</t>
+          <t>2025-05-09</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-04-18</t>
+          <t>2025-05-09</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3099,58 +2978,43 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>Hår, päls, fjäll eller fjädrar</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Hair, fur, scale or feather</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124199083</v>
+        <v>124896056</v>
       </c>
       <c r="B24" t="n">
-        <v>57883</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103015</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3161,19 +3025,19 @@
       <c r="I24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Kungsfågel, Mpd</t>
+          <t>Övertjärnen, Övertjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>596036</v>
+        <v>595986</v>
       </c>
       <c r="R24" t="n">
-        <v>6928364</v>
+        <v>6928304</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3200,12 +3064,27 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-04-18</t>
+          <t>2025-05-09</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-04-18</t>
+          <t>2025-05-09</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3220,27 +3099,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124199280</v>
+        <v>126626263</v>
       </c>
       <c r="B25" t="n">
-        <v>57666</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3248,42 +3122,42 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Talltita, Mpd</t>
+          <t>Spillkråka, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>596095</v>
+        <v>595866</v>
       </c>
       <c r="R25" t="n">
-        <v>6928397</v>
+        <v>6928388</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3307,12 +3181,17 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-04-18</t>
+          <t>2025-07-13</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-04-18</t>
+          <t>2025-07-13</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3339,50 +3218,50 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124186575</v>
+        <v>124191655</v>
       </c>
       <c r="B26" t="n">
-        <v>79891</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Lynglav, Mpd</t>
+          <t>Tjäder , Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>596036</v>
+        <v>595903</v>
       </c>
       <c r="R26" t="n">
-        <v>6928364</v>
+        <v>6928353</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3412,9 +3291,19 @@
           <t>2025-04-18</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-04-18</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3429,27 +3318,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124247686</v>
+        <v>124192837</v>
       </c>
       <c r="B27" t="n">
-        <v>56722</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3474,33 +3358,17 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Tjäder hona fjäder, Näsvattnet, Sättna, Mpd</t>
+          <t>Talltita , Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>595862</v>
+        <v>595923</v>
       </c>
       <c r="R27" t="n">
-        <v>6928373</v>
+        <v>6928341</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3527,17 +3395,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-04-19</t>
+          <t>2025-04-18</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-04-19</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Tjäder hona fjäder</t>
+          <t>2025-04-18</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3564,65 +3437,50 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124247642</v>
+        <v>124193338</v>
       </c>
       <c r="B28" t="n">
-        <v>57681</v>
+        <v>57141</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Spillkråka fjäder, Näsvattnet, Sättna, Mpd</t>
+          <t>Tjäder , Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>595933</v>
+        <v>595945</v>
       </c>
       <c r="R28" t="n">
-        <v>6928381</v>
+        <v>6928357</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3649,17 +3507,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-04-19</t>
+          <t>2025-04-18</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-04-19</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Tappad blodfjäder av Spillkråka. Spillkråkan har även observerats och hörts inom området vid upprepade olika tillfällen.</t>
+          <t>2025-04-18</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3686,44 +3549,35 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124246445</v>
+        <v>124198508</v>
       </c>
       <c r="B29" t="n">
-        <v>57666</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
         <is>
           <t>adult</t>
@@ -3731,32 +3585,22 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>bobygge</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>hane</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Talltita x2, Näsvattnet, Sättna, Mpd</t>
+          <t>Tjäderfjäder, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>596137</v>
+        <v>596067</v>
       </c>
       <c r="R29" t="n">
-        <v>6928347</v>
+        <v>6928345</v>
       </c>
       <c r="S29" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3780,17 +3624,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-04-19</t>
+          <t>2025-04-18</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-04-19</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Två talltitor bygger ett bo i skogen när jag kommer gåendes är dom först väldigt upprörda och varnar, dom vill ha bort mig där ifrån. Lämnar dom ifred och sätter mig en bit där ifrån då upptar dom bobygget.</t>
+          <t>2025-04-18</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3801,82 +3640,86 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>Hår, päls, fjäll eller fjädrar</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Hair, fur, scale or feather</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124246681</v>
+        <v>124201844</v>
       </c>
       <c r="B30" t="n">
-        <v>57666</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="K30" t="inlineStr">
         <is>
           <t>adult</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr"/>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Talltita, Näsvattnet, Sättna, Mpd</t>
+          <t>Tjäder, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>596108</v>
+        <v>596216</v>
       </c>
       <c r="R30" t="n">
-        <v>6928344</v>
+        <v>6928367</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3903,17 +3746,22 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-04-19</t>
+          <t>2025-04-18</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-04-19</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>2025-04-18</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3940,50 +3788,61 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124894505</v>
+        <v>124247686</v>
       </c>
       <c r="B31" t="n">
-        <v>57681</v>
+        <v>57141</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Mellantjärn, Mpd</t>
+          <t>Tjäder hona fjäder, Näsvattnet, Sättna, Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>596123</v>
+        <v>595862</v>
       </c>
       <c r="R31" t="n">
-        <v>6928363</v>
+        <v>6928373</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4010,22 +3869,17 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>13:37</t>
+          <t>2025-04-19</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>13:37</t>
+          <t>2025-04-19</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Tjäder hona fjäder</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4040,57 +3894,62 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124894635</v>
+        <v>124201216</v>
       </c>
       <c r="B32" t="n">
-        <v>78947</v>
+        <v>57132</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Mellantjärn, Mpd</t>
+          <t>Järpe , Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>596094</v>
+        <v>596199</v>
       </c>
       <c r="R32" t="n">
-        <v>6928363</v>
+        <v>6928355</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4117,22 +3976,22 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-04-18</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-04-18</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4147,57 +4006,57 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124895163</v>
+        <v>124201656</v>
       </c>
       <c r="B33" t="n">
-        <v>80028</v>
+        <v>57132</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>102612</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Mellantjärn, Mpd</t>
+          <t>Järpebajs, Mpd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>596123</v>
+        <v>596201</v>
       </c>
       <c r="R33" t="n">
-        <v>6928363</v>
+        <v>6928367</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4224,22 +4083,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>14:00</t>
+          <t>2025-04-18</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>14:00</t>
+          <t>2025-04-18</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4250,6 +4099,16 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>Spillning</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Dropping</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
@@ -4266,27 +4125,27 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124895718</v>
+        <v>124190248</v>
       </c>
       <c r="B34" t="n">
-        <v>57741</v>
+        <v>57144</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>102613</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -4297,19 +4156,19 @@
       <c r="I34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Mellantjärn, Mellantjärn, Mpd</t>
+          <t>Knärot, Mpd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>596031</v>
+        <v>595770</v>
       </c>
       <c r="R34" t="n">
-        <v>6928336</v>
+        <v>6928377</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4336,27 +4195,22 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-04-18</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-04-18</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:15</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4371,22 +4225,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124896591</v>
+        <v>124189689</v>
       </c>
       <c r="B35" t="n">
-        <v>91459</v>
+        <v>58393</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4394,34 +4248,39 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>658</v>
+        <v>102999</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Övertjärnen, Övertjärnen, Mpd</t>
+          <t>Björktrast, Mpd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>595901</v>
+        <v>595952</v>
       </c>
       <c r="R35" t="n">
-        <v>6928407</v>
+        <v>6928371</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4448,22 +4307,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>14:47</t>
+          <t>2025-04-18</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>14:47</t>
+          <t>2025-04-18</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4478,22 +4327,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124895047</v>
+        <v>124188895</v>
       </c>
       <c r="B36" t="n">
-        <v>57741</v>
+        <v>58388</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4501,39 +4350,39 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>103001</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Mellantjärnen, Mellantjärnen, Mpd</t>
+          <t>Rödvingetrast, Mpd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>596113</v>
+        <v>595997</v>
       </c>
       <c r="R36" t="n">
-        <v>6928348</v>
+        <v>6928324</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4560,27 +4409,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>13:55</t>
+          <t>2025-04-18</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>13:55</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>2025-04-18</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4595,54 +4429,59 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124893384</v>
+        <v>124199083</v>
       </c>
       <c r="B37" t="n">
-        <v>80028</v>
+        <v>58327</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>103015</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Mellantjärn, Mpd</t>
+          <t>Kungsfågel, Mpd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>596135</v>
+        <v>596036</v>
       </c>
       <c r="R37" t="n">
         <v>6928364</v>
@@ -4672,22 +4511,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>13:05</t>
+          <t>2025-04-18</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>13:05</t>
+          <t>2025-04-18</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4702,65 +4531,75 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126626263</v>
+        <v>125011151</v>
       </c>
       <c r="B38" t="n">
-        <v>57741</v>
+        <v>58439</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>103018</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Spillkråka, Mpd</t>
+          <t>Övertjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>595866</v>
+        <v>595936</v>
       </c>
       <c r="R38" t="n">
-        <v>6928388</v>
+        <v>6928421</v>
       </c>
       <c r="S38" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4784,17 +4623,27 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-07-13</t>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-07-13</t>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Fångar mygg i luften nyfiken på oss.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4809,15 +4658,1669 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>124191705</v>
+      </c>
+      <c r="B39" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Talltita , Mpd</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>595923</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6928341</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Sättna</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-04-18</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>11:42</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-04-18</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>11:42</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>2 talltita kan höras i träden</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>124199280</v>
+      </c>
+      <c r="B40" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Talltita, Mpd</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>596095</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6928397</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Sättna</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-04-18</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-04-18</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
           <t>Joel Helker-Nygren</t>
         </is>
       </c>
-      <c r="AX38" t="inlineStr">
+      <c r="AX40" t="inlineStr">
         <is>
           <t>Joel Helker-Nygren</t>
         </is>
       </c>
-      <c r="AY38" t="inlineStr"/>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>124246445</v>
+      </c>
+      <c r="B41" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>bobygge</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Talltita x2, Näsvattnet, Sättna, Mpd</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>596137</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6928347</v>
+      </c>
+      <c r="S41" t="n">
+        <v>25</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Sättna</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-04-19</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-04-19</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Två talltitor bygger ett bo i skogen när jag kommer gåendes är dom först väldigt upprörda och varnar, dom vill ha bort mig där ifrån. Lämnar dom ifred och sätter mig en bit där ifrån då upptar dom bobygget.</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>124246681</v>
+      </c>
+      <c r="B42" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Talltita, Näsvattnet, Sättna, Mpd</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>596108</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6928344</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Sättna</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-04-19</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-04-19</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>125011148</v>
+      </c>
+      <c r="B43" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Övertjärnen, Övertjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>595968</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6928409</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Sättna</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>13:08</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>13:08</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>124896131</v>
+      </c>
+      <c r="B44" t="n">
+        <v>56522</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>206004</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Skogshare</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Lepus timidus</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Övertjärnen, Övertjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>595978</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6928306</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Sättna</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-05-09</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-05-09</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>124189989</v>
+      </c>
+      <c r="B45" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Knärot, Mpd</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>595770</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6928377</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Sättna</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-04-18</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-04-18</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>124190645</v>
+      </c>
+      <c r="B46" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Knärot , Mpd</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>595796</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6928382</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Sättna</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-04-18</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-04-18</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>124193487</v>
+      </c>
+      <c r="B47" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Garnlav , Mpd</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>595943</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6928393</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Sättna</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-04-18</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-04-18</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>124895455</v>
+      </c>
+      <c r="B48" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Mellantjärnen, Mellantjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>596081</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6928322</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Sättna</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-05-09</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>14:07</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-05-09</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>14:07</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Knärot på hyggeskant</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>105899115</v>
+      </c>
+      <c r="B49" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Tjärdalsberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>596139</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6928345</v>
+      </c>
+      <c r="S49" t="n">
+        <v>25</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Sättna</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2022-09-14</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2022-09-14</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Dennis Jonason</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Dennis Jonason</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>105899116</v>
+      </c>
+      <c r="B50" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Tjärdalsberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>596020</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6928373</v>
+      </c>
+      <c r="S50" t="n">
+        <v>25</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Sättna</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2022-09-14</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2022-09-14</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Dennis Jonason</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Dennis Jonason</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>124185717</v>
+      </c>
+      <c r="B51" t="n">
+        <v>79328</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>230405</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Garnlav (ssp. sarmentosa)</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Garnlav , Mpd</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>595943</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6928393</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Sättna</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-04-18</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>09:33</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-04-18</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>09:33</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>124197321</v>
+      </c>
+      <c r="B52" t="n">
+        <v>79328</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>230405</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Garnlav (ssp. sarmentosa)</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>garnlav , Mpd</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>596021</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6928323</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Sättna</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-04-18</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>13:18</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-04-18</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>13:18</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>124206962</v>
+      </c>
+      <c r="B53" t="n">
+        <v>58121</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>266237</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Talltita x tofsmes</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Poecile montanus x Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Större hackspett , Mpd</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>596168</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6928357</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Sättna</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-04-18</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-04-18</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 21662-2022 artfynd.xlsx
+++ b/artfynd/A 21662-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY53"/>
+  <dimension ref="A1:AZ53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105899083</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105899084</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -973,6 +988,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124896591</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,6 +1100,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124896614</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124185899</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1274,6 +1304,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105899200</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1371,6 +1406,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124186575</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1473,6 +1513,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124120714</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1595,6 +1640,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124247642</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1712,6 +1762,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124895718</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1829,6 +1884,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124895747</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1946,6 +2006,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124896056</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2053,6 +2118,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126626263</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2165,6 +2235,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124191655</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2272,6 +2347,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124192837</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2384,6 +2464,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124193338</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2502,6 +2587,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124247686</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2614,6 +2704,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124190248</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2716,6 +2811,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124189689</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2818,6 +2918,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124188895</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2920,6 +3025,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124199083</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3047,6 +3157,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125011151</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3159,6 +3274,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124191705</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3280,6 +3400,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125011148</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3392,6 +3517,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124896131</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3499,6 +3629,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124189989</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3606,6 +3741,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124190645</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3713,6 +3853,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124193487</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3810,6 +3955,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105899116</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3917,6 +4067,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124185717</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4024,6 +4179,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124197321</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4121,6 +4281,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124201987</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4218,6 +4383,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105899198</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4315,6 +4485,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105899199</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4425,6 +4600,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124247923</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4532,6 +4712,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124894635</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4629,6 +4814,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124128891</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4736,6 +4926,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124893384</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4843,6 +5038,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124895163</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4955,6 +5155,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124894505</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5069,6 +5274,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124138703</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5186,6 +5396,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124895047</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5303,6 +5518,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124198508</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5425,6 +5645,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124201844</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5537,6 +5762,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124201216</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5644,6 +5874,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124201656</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5746,6 +5981,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124199280</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5872,6 +6112,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124246445</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5990,6 +6235,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124246681</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6111,6 +6361,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124895455</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6208,6 +6463,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105899115</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6321,8 +6581,67 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124206962</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>